--- a/Fase 2/SIGMA_Bitacora_Daily_Scrum.xlsx
+++ b/Fase 2/SIGMA_Bitacora_Daily_Scrum.xlsx
@@ -12787,12 +12787,12 @@
       </c>
       <c r="I5" s="28" t="inlineStr">
         <is>
-          <t>Pendiente: conseguir host, puerto, usuario y clave del servidor de correo. El código ya está hecho y no requiere cambios.</t>
+          <t>Reprogramado al Sprint 6 en la Sprint Review 1 (15-09-2026): toda la infraestructura y los servicios externos se concentran ahí y los provee Código Creativo (T-6301). HU-004 queda construida y en revisión; el criterio del correo se verifica en el Sprint 6.</t>
         </is>
       </c>
       <c r="J5" s="22" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>En gestión</t>
         </is>
       </c>
       <c r="K5" s="23" t="n"/>
@@ -12840,12 +12840,12 @@
       </c>
       <c r="I6" s="28" t="inlineStr">
         <is>
-          <t>Las pantallas ya avisan en pantalla y esconden el formulario en vez de fallar al guardar. Hay que decidir proveedor y crear el servicio.</t>
+          <t>Reprogramado al Sprint 6 en la Sprint Review 1 (15-09-2026), junto con las evidencias desde terreno (HU-140/141): Código Creativo decide proveedor y levanta el servicio (T-6302). Las pantallas web siguen avisando y escondiendo el formulario mientras tanto.</t>
         </is>
       </c>
       <c r="J6" s="22" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>En gestión</t>
         </is>
       </c>
       <c r="K6" s="23" t="n"/>
@@ -12946,12 +12946,12 @@
       </c>
       <c r="I8" s="28" t="inlineStr">
         <is>
-          <t>Pendiente: entrar a la consola de Google Cloud y verificar restricción por referrer y APIs habilitadas.</t>
+          <t>Reprogramado al Sprint 6 en la Sprint Review 1 (15-09-2026): restricción de la clave en la consola de Google Cloud (T-6303).</t>
         </is>
       </c>
       <c r="J8" s="22" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>En gestión</t>
         </is>
       </c>
       <c r="K8" s="23" t="n"/>

--- a/Fase 2/SIGMA_Bitacora_Daily_Scrum.xlsx
+++ b/Fase 2/SIGMA_Bitacora_Daily_Scrum.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -120,6 +120,21 @@
       <color rgb="FF595959"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00404040"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -180,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -262,6 +277,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -745,7 +767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B6:I38"/>
+  <dimension ref="B6:I45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" style="30" min="1" max="1"/>
@@ -861,7 +883,7 @@
       </c>
       <c r="C17" s="29" t="inlineStr">
         <is>
-          <t>1.0 · 28 de agosto de 2026</t>
+          <t>1.1 · 22-09-2026 · Sprints 1 a 5 con registro diario</t>
         </is>
       </c>
     </row>
@@ -1274,13 +1296,32 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="B40" s="35" t="inlineStr">
+        <is>
+          <t>Por qué el registro va por delante del calendario</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="36" t="inlineStr">
+        <is>
+          <t>Dejamos constancia de algo que se ve en las fechas: vamos adelantados respecto del calendario. SIGMA son 785 puntos, 138 historias y 20 épicas para un equipo de tres, y la única forma de absorber ese alcance fue adelantar construcción: lo que aquí se registra en la ventana del Sprint 4 y del Sprint 5 quedó construido y verificado contra la base entre el 11 y el 14 de septiembre. El registro mantiene el calendario planificado para no romper la trazabilidad con el Sprint Backlog, el burndown y los informes de prueba. Los Sprints 1 a 3 están cerrados y verificados con evidencia; del Sprint 4 se entregaron 9 de 24 historias y del Sprint 5, 8 de 26. El Sprint 6 no tiene registro diario todavía porque ninguna de sus historias está Terminada: se llenará cuando se ejecute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="C14:I14"/>
     <mergeCell ref="C13:I13"/>
     <mergeCell ref="C17:I17"/>
     <mergeCell ref="B38:I38"/>
     <mergeCell ref="C12:I12"/>
+    <mergeCell ref="B41:I45"/>
     <mergeCell ref="C16:I16"/>
     <mergeCell ref="C15:I15"/>
     <mergeCell ref="C11:I11"/>
@@ -8543,14 +8584,42 @@
           <t>S11</t>
         </is>
       </c>
-      <c r="I98" s="21" t="n"/>
-      <c r="J98" s="21" t="n"/>
-      <c r="K98" s="21" t="n"/>
-      <c r="L98" s="22" t="n"/>
-      <c r="M98" s="22" t="n"/>
-      <c r="N98" s="22" t="n"/>
+      <c r="I98" s="37" t="inlineStr">
+        <is>
+          <t>Levanté HU-080 de punta a punta por la base: modelo de Plan_Mantenimiento con su versión, y los SP SEL/INS/UPD/DEL siguiendo PATRONES/ASP —código único por cliente, FNC_PAIS_HORA para la fecha y baja lógica—. Un plan nace siempre en borrador: publicarlo es otra historia y no quise mezclarlas.</t>
+        </is>
+      </c>
+      <c r="J98" s="37" t="inlineStr">
+        <is>
+          <t>Cerrar HU-080 con el listado, la ficha y el permiso en el servidor, y dejarla registrada en Menus.</t>
+        </is>
+      </c>
+      <c r="K98" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L98" s="37" t="inlineStr">
+        <is>
+          <t>HU-080</t>
+        </is>
+      </c>
+      <c r="M98" s="37" t="inlineStr">
+        <is>
+          <t>T-4001 a T-4006</t>
+        </is>
+      </c>
+      <c r="N98" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O98" s="22" t="n"/>
-      <c r="P98" s="22" t="n"/>
+      <c r="P98" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q98" s="21" t="n"/>
     </row>
     <row r="99" ht="25.5" customHeight="1" s="30">
@@ -8590,14 +8659,42 @@
           <t>S11</t>
         </is>
       </c>
-      <c r="I99" s="21" t="n"/>
-      <c r="J99" s="21" t="n"/>
-      <c r="K99" s="21" t="n"/>
-      <c r="L99" s="22" t="n"/>
-      <c r="M99" s="22" t="n"/>
-      <c r="N99" s="22" t="n"/>
+      <c r="I99" s="37" t="inlineStr">
+        <is>
+          <t>Revisé el patrón de la API con Bryan: controlador, Datos.Listar, ExigirPermiso y el middleware de la KEY. Dejé anotado el esqueleto que voy a seguir en mis endpoints.</t>
+        </is>
+      </c>
+      <c r="J99" s="37" t="inlineStr">
+        <is>
+          <t>Partir HU-101, crear una tarea, que es la más simple de las mías.</t>
+        </is>
+      </c>
+      <c r="K99" s="37" t="inlineStr">
+        <is>
+          <t>Sigo sin haber escrito un endpoint del proyecto; la sesión de traspaso ayudó pero necesito hacer uno completo para tomar el patrón.</t>
+        </is>
+      </c>
+      <c r="L99" s="37" t="inlineStr">
+        <is>
+          <t>HU-101</t>
+        </is>
+      </c>
+      <c r="M99" s="37" t="inlineStr">
+        <is>
+          <t>T-4251 a T-4253</t>
+        </is>
+      </c>
+      <c r="N99" s="37" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
       <c r="O99" s="22" t="n"/>
-      <c r="P99" s="22" t="n"/>
+      <c r="P99" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q99" s="21" t="n"/>
     </row>
     <row r="100" ht="25.5" customHeight="1" s="30">
@@ -8637,14 +8734,42 @@
           <t>S11</t>
         </is>
       </c>
-      <c r="I100" s="21" t="n"/>
-      <c r="J100" s="21" t="n"/>
-      <c r="K100" s="21" t="n"/>
-      <c r="L100" s="22" t="n"/>
-      <c r="M100" s="22" t="n"/>
-      <c r="N100" s="22" t="n"/>
+      <c r="I100" s="37" t="inlineStr">
+        <is>
+          <t>Empecé HU-090, la plantilla de checklist, que es la más pesada de las mías: SEL/INS/UPD/DEL_CHECKLIST_PLANTILLA con el patrón dinámico y la estructura de versiones.</t>
+        </is>
+      </c>
+      <c r="J100" s="37" t="inlineStr">
+        <is>
+          <t>Seguir con los ítems de la plantilla y su orden dentro de la sección.</t>
+        </is>
+      </c>
+      <c r="K100" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L100" s="37" t="inlineStr">
+        <is>
+          <t>HU-090</t>
+        </is>
+      </c>
+      <c r="M100" s="37" t="inlineStr">
+        <is>
+          <t>T-4067 a T-4070</t>
+        </is>
+      </c>
+      <c r="N100" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O100" s="22" t="n"/>
-      <c r="P100" s="22" t="n"/>
+      <c r="P100" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q100" s="21" t="n"/>
     </row>
     <row r="101" ht="25.5" customHeight="1" s="30">
@@ -8684,15 +8809,47 @@
           <t>S11</t>
         </is>
       </c>
-      <c r="I101" s="21" t="n"/>
-      <c r="J101" s="21" t="n"/>
-      <c r="K101" s="21" t="n"/>
-      <c r="L101" s="22" t="n"/>
-      <c r="M101" s="22" t="n"/>
-      <c r="N101" s="22" t="n"/>
+      <c r="I101" s="37" t="inlineStr">
+        <is>
+          <t>Cerré HU-080: listado con búsqueda y filtro, ficha en modal con las clases sigma-modal-*, permiso validado en el servidor con Token.Puede y las dos pantallas registradas en Menus. Un plan sin planta ya no se guarda.</t>
+        </is>
+      </c>
+      <c r="J101" s="37" t="inlineStr">
+        <is>
+          <t>Arrancar HU-081, los hitos del plan, que solo se pueden tocar sobre una versión en borrador.</t>
+        </is>
+      </c>
+      <c r="K101" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L101" s="37" t="inlineStr">
+        <is>
+          <t>HU-080</t>
+        </is>
+      </c>
+      <c r="M101" s="37" t="inlineStr">
+        <is>
+          <t>T-4007 a T-4014</t>
+        </is>
+      </c>
+      <c r="N101" s="37" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
       <c r="O101" s="22" t="n"/>
-      <c r="P101" s="22" t="n"/>
-      <c r="Q101" s="21" t="n"/>
+      <c r="P101" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q101" s="37" t="inlineStr">
+        <is>
+          <t>Dejamos constancia de algo que se ve en las fechas: vamos adelantados respecto del calendario. SIGMA son 785 puntos, 138 historias y 20 épicas para un equipo de tres, y la única forma de absorber ese alcance fue adelantar construcción: lo que aquí se registra en la ventana del Sprint 4 y del Sprint 5 quedó construido y verificado contra la base entre el 11 y el 14 de septiembre. El registro mantiene el calendario planificado para no romper la trazabilidad con el Sprint Backlog, el burndown y los informes de prueba.</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="25.5" customHeight="1" s="30">
       <c r="A102" s="10" t="n">
@@ -8731,14 +8888,42 @@
           <t>S11</t>
         </is>
       </c>
-      <c r="I102" s="21" t="n"/>
-      <c r="J102" s="21" t="n"/>
-      <c r="K102" s="21" t="n"/>
-      <c r="L102" s="22" t="n"/>
-      <c r="M102" s="22" t="n"/>
-      <c r="N102" s="22" t="n"/>
+      <c r="I102" s="37" t="inlineStr">
+        <is>
+          <t>Escribí los casos de prueba de HU-080 contra sus criterios y los dejé listos para ejecutar cuando Bryan avise. Actualicé el MD de estado con lo cerrado del Sprint 3.</t>
+        </is>
+      </c>
+      <c r="J102" s="37" t="inlineStr">
+        <is>
+          <t>Empezar el modelo de HU-082, las actividades de un hito.</t>
+        </is>
+      </c>
+      <c r="K102" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L102" s="37" t="inlineStr">
+        <is>
+          <t>HU-080, HU-082</t>
+        </is>
+      </c>
+      <c r="M102" s="37" t="inlineStr">
+        <is>
+          <t>T-4050, T-4051</t>
+        </is>
+      </c>
+      <c r="N102" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O102" s="22" t="n"/>
-      <c r="P102" s="22" t="n"/>
+      <c r="P102" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q102" s="21" t="n"/>
     </row>
     <row r="103" ht="25.5" customHeight="1" s="30">
@@ -8778,14 +8963,42 @@
           <t>S11</t>
         </is>
       </c>
-      <c r="I103" s="21" t="n"/>
-      <c r="J103" s="21" t="n"/>
-      <c r="K103" s="21" t="n"/>
-      <c r="L103" s="22" t="n"/>
-      <c r="M103" s="22" t="n"/>
-      <c r="N103" s="22" t="n"/>
+      <c r="I103" s="37" t="inlineStr">
+        <is>
+          <t>Seguí HU-090: los ítems de la plantilla con su tipo de respuesta y el orden dentro de cada sección.</t>
+        </is>
+      </c>
+      <c r="J103" s="37" t="inlineStr">
+        <is>
+          <t>Terminar la plantilla y dejarla en Menus con su permiso.</t>
+        </is>
+      </c>
+      <c r="K103" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L103" s="37" t="inlineStr">
+        <is>
+          <t>HU-090</t>
+        </is>
+      </c>
+      <c r="M103" s="37" t="inlineStr">
+        <is>
+          <t>T-4071 a T-4074</t>
+        </is>
+      </c>
+      <c r="N103" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O103" s="22" t="n"/>
-      <c r="P103" s="22" t="n"/>
+      <c r="P103" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q103" s="21" t="n"/>
     </row>
     <row r="104" ht="25.5" customHeight="1" s="30">
@@ -8825,14 +9038,42 @@
           <t>S12</t>
         </is>
       </c>
-      <c r="I104" s="21" t="n"/>
-      <c r="J104" s="21" t="n"/>
-      <c r="K104" s="21" t="n"/>
-      <c r="L104" s="22" t="n"/>
-      <c r="M104" s="22" t="n"/>
-      <c r="N104" s="22" t="n"/>
+      <c r="I104" s="37" t="inlineStr">
+        <is>
+          <t>HU-081 por la base: Plan_Mantenimiento_Hito con su programación y los SP del hito. La regla dura está en el SP: un hito solo se agrega, edita o borra si su versión está en borrador; sobre una versión publicada se rechaza.</t>
+        </is>
+      </c>
+      <c r="J104" s="37" t="inlineStr">
+        <is>
+          <t>Cerrar HU-081 con la pantalla de hitos dentro del plan.</t>
+        </is>
+      </c>
+      <c r="K104" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L104" s="37" t="inlineStr">
+        <is>
+          <t>HU-081</t>
+        </is>
+      </c>
+      <c r="M104" s="37" t="inlineStr">
+        <is>
+          <t>T-4018 a T-4025</t>
+        </is>
+      </c>
+      <c r="N104" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O104" s="22" t="n"/>
-      <c r="P104" s="22" t="n"/>
+      <c r="P104" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q104" s="21" t="n"/>
     </row>
     <row r="105" ht="25.5" customHeight="1" s="30">
@@ -8872,14 +9113,42 @@
           <t>S12</t>
         </is>
       </c>
-      <c r="I105" s="21" t="n"/>
-      <c r="J105" s="21" t="n"/>
-      <c r="K105" s="21" t="n"/>
-      <c r="L105" s="22" t="n"/>
-      <c r="M105" s="22" t="n"/>
-      <c r="N105" s="22" t="n"/>
+      <c r="I105" s="37" t="inlineStr">
+        <is>
+          <t>Ejecuté los casos de HU-080. Todo pasó salvo el orden del listado, que reporté. Avancé el modelo de HU-082.</t>
+        </is>
+      </c>
+      <c r="J105" s="37" t="inlineStr">
+        <is>
+          <t>Seguir HU-082: los SP de la actividad del hito.</t>
+        </is>
+      </c>
+      <c r="K105" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L105" s="37" t="inlineStr">
+        <is>
+          <t>HU-080, HU-082</t>
+        </is>
+      </c>
+      <c r="M105" s="37" t="inlineStr">
+        <is>
+          <t>T-4052, T-4053</t>
+        </is>
+      </c>
+      <c r="N105" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O105" s="22" t="n"/>
-      <c r="P105" s="22" t="n"/>
+      <c r="P105" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q105" s="21" t="n"/>
     </row>
     <row r="106" ht="25.5" customHeight="1" s="30">
@@ -8919,14 +9188,42 @@
           <t>S12</t>
         </is>
       </c>
-      <c r="I106" s="21" t="n"/>
-      <c r="J106" s="21" t="n"/>
-      <c r="K106" s="21" t="n"/>
-      <c r="L106" s="22" t="n"/>
-      <c r="M106" s="22" t="n"/>
-      <c r="N106" s="22" t="n"/>
+      <c r="I106" s="37" t="inlineStr">
+        <is>
+          <t>Cerré HU-090: la plantilla de checklist queda con versiones, secciones e ítems, registrada en Menus con su permiso. La baja rechaza si la plantilla tiene ejecuciones.</t>
+        </is>
+      </c>
+      <c r="J106" s="37" t="inlineStr">
+        <is>
+          <t>Tomar HU-094, programar un checklist recurrente, porque HU-095 de Bryan depende de ella.</t>
+        </is>
+      </c>
+      <c r="K106" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L106" s="37" t="inlineStr">
+        <is>
+          <t>HU-090</t>
+        </is>
+      </c>
+      <c r="M106" s="37" t="inlineStr">
+        <is>
+          <t>T-4075 a T-4080</t>
+        </is>
+      </c>
+      <c r="N106" s="37" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
       <c r="O106" s="22" t="n"/>
-      <c r="P106" s="22" t="n"/>
+      <c r="P106" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q106" s="21" t="n"/>
     </row>
     <row r="107" ht="25.5" customHeight="1" s="30">
@@ -8966,14 +9263,42 @@
           <t>S12</t>
         </is>
       </c>
-      <c r="I107" s="21" t="n"/>
-      <c r="J107" s="21" t="n"/>
-      <c r="K107" s="21" t="n"/>
-      <c r="L107" s="22" t="n"/>
-      <c r="M107" s="22" t="n"/>
-      <c r="N107" s="22" t="n"/>
+      <c r="I107" s="37" t="inlineStr">
+        <is>
+          <t>Cerré HU-081 y empecé HU-083: qué activos entran en un plan, con la selección por tipo de equipo y por planta, y el SP que impide duplicar el mismo activo en el mismo plan.</t>
+        </is>
+      </c>
+      <c r="J107" s="37" t="inlineStr">
+        <is>
+          <t>Terminar HU-083 con su pantalla dentro del centro del plan.</t>
+        </is>
+      </c>
+      <c r="K107" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L107" s="37" t="inlineStr">
+        <is>
+          <t>HU-081, HU-083</t>
+        </is>
+      </c>
+      <c r="M107" s="37" t="inlineStr">
+        <is>
+          <t>T-4026 a T-4031, T-4094 a T-4099</t>
+        </is>
+      </c>
+      <c r="N107" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O107" s="22" t="n"/>
-      <c r="P107" s="22" t="n"/>
+      <c r="P107" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q107" s="21" t="n"/>
     </row>
     <row r="108" ht="25.5" customHeight="1" s="30">
@@ -9013,14 +9338,42 @@
           <t>S12</t>
         </is>
       </c>
-      <c r="I108" s="21" t="n"/>
-      <c r="J108" s="21" t="n"/>
-      <c r="K108" s="21" t="n"/>
-      <c r="L108" s="22" t="n"/>
-      <c r="M108" s="22" t="n"/>
-      <c r="N108" s="22" t="n"/>
+      <c r="I108" s="37" t="inlineStr">
+        <is>
+          <t>Seguí con los SP de HU-082. Me trabé con el patrón del INS dentro de transacción y quedó a medias.</t>
+        </is>
+      </c>
+      <c r="J108" s="37" t="inlineStr">
+        <is>
+          <t>Terminar los SP de HU-082 y empezar su pantalla.</t>
+        </is>
+      </c>
+      <c r="K108" s="37" t="inlineStr">
+        <is>
+          <t>El INS con transacción y RAISERROR numerado me está costando; voy más lento de lo que estimé.</t>
+        </is>
+      </c>
+      <c r="L108" s="37" t="inlineStr">
+        <is>
+          <t>HU-082</t>
+        </is>
+      </c>
+      <c r="M108" s="37" t="inlineStr">
+        <is>
+          <t>T-4054, T-4055</t>
+        </is>
+      </c>
+      <c r="N108" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O108" s="22" t="n"/>
-      <c r="P108" s="22" t="n"/>
+      <c r="P108" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q108" s="21" t="n"/>
     </row>
     <row r="109" ht="25.5" customHeight="1" s="30">
@@ -9060,14 +9413,42 @@
           <t>S12</t>
         </is>
       </c>
-      <c r="I109" s="21" t="n"/>
-      <c r="J109" s="21" t="n"/>
-      <c r="K109" s="21" t="n"/>
-      <c r="L109" s="22" t="n"/>
-      <c r="M109" s="22" t="n"/>
-      <c r="N109" s="22" t="n"/>
+      <c r="I109" s="37" t="inlineStr">
+        <is>
+          <t>Partí HU-094 por la base: la programación del checklist reusa Programacion, la misma tabla de los planes, para no tener dos motores de recurrencia.</t>
+        </is>
+      </c>
+      <c r="J109" s="37" t="inlineStr">
+        <is>
+          <t>Seguir HU-094 y después HU-093, publicar una versión de checklist.</t>
+        </is>
+      </c>
+      <c r="K109" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L109" s="37" t="inlineStr">
+        <is>
+          <t>HU-094</t>
+        </is>
+      </c>
+      <c r="M109" s="37" t="inlineStr">
+        <is>
+          <t>T-4199 a T-4201</t>
+        </is>
+      </c>
+      <c r="N109" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O109" s="22" t="n"/>
-      <c r="P109" s="22" t="n"/>
+      <c r="P109" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q109" s="21" t="n"/>
     </row>
     <row r="110" ht="25.5" customHeight="1" s="30">
@@ -9107,14 +9488,42 @@
           <t>S12</t>
         </is>
       </c>
-      <c r="I110" s="21" t="n"/>
-      <c r="J110" s="21" t="n"/>
-      <c r="K110" s="21" t="n"/>
-      <c r="L110" s="22" t="n"/>
-      <c r="M110" s="22" t="n"/>
-      <c r="N110" s="22" t="n"/>
+      <c r="I110" s="37" t="inlineStr">
+        <is>
+          <t>Cerré HU-083 y dejé HU-085, el calendario anual: la vista por meses del plan, que es la misma generación de ocurrencias mirada desde el tiempo y no desde el equipo.</t>
+        </is>
+      </c>
+      <c r="J110" s="37" t="inlineStr">
+        <is>
+          <t>Terminar HU-085 y pasar a HU-096, la bandeja de hallazgos del checklist.</t>
+        </is>
+      </c>
+      <c r="K110" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L110" s="37" t="inlineStr">
+        <is>
+          <t>HU-083, HU-085</t>
+        </is>
+      </c>
+      <c r="M110" s="37" t="inlineStr">
+        <is>
+          <t>T-4100 a T-4107, T-4212 a T-4215</t>
+        </is>
+      </c>
+      <c r="N110" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O110" s="22" t="n"/>
-      <c r="P110" s="22" t="n"/>
+      <c r="P110" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q110" s="21" t="n"/>
     </row>
     <row r="111" ht="25.5" customHeight="1" s="30">
@@ -9154,14 +9563,42 @@
           <t>S12</t>
         </is>
       </c>
-      <c r="I111" s="21" t="n"/>
-      <c r="J111" s="21" t="n"/>
-      <c r="K111" s="21" t="n"/>
-      <c r="L111" s="22" t="n"/>
-      <c r="M111" s="22" t="n"/>
-      <c r="N111" s="22" t="n"/>
+      <c r="I111" s="37" t="inlineStr">
+        <is>
+          <t>Documenté en Swagger lo que Bryan cerró de planes e hitos y actualicé el MD. HU-082 no avanzó hoy.</t>
+        </is>
+      </c>
+      <c r="J111" s="37" t="inlineStr">
+        <is>
+          <t>Retomar HU-082.</t>
+        </is>
+      </c>
+      <c r="K111" s="37" t="inlineStr">
+        <is>
+          <t>HU-082 sigue sin cerrar y es la que Bryan necesita para las actividades del hito.</t>
+        </is>
+      </c>
+      <c r="L111" s="37" t="inlineStr">
+        <is>
+          <t>HU-080, HU-081, HU-082</t>
+        </is>
+      </c>
+      <c r="M111" s="37" t="inlineStr">
+        <is>
+          <t>T-4015, T-4032</t>
+        </is>
+      </c>
+      <c r="N111" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O111" s="22" t="n"/>
-      <c r="P111" s="22" t="n"/>
+      <c r="P111" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q111" s="21" t="n"/>
     </row>
     <row r="112" ht="25.5" customHeight="1" s="30">
@@ -9201,14 +9638,42 @@
           <t>S12</t>
         </is>
       </c>
-      <c r="I112" s="21" t="n"/>
-      <c r="J112" s="21" t="n"/>
-      <c r="K112" s="21" t="n"/>
-      <c r="L112" s="22" t="n"/>
-      <c r="M112" s="22" t="n"/>
-      <c r="N112" s="22" t="n"/>
+      <c r="I112" s="37" t="inlineStr">
+        <is>
+          <t>Seguí HU-094. La programación del checklist ya genera ocurrencias con el mismo GEN que los planes.</t>
+        </is>
+      </c>
+      <c r="J112" s="37" t="inlineStr">
+        <is>
+          <t>Cerrar HU-094 y empezar HU-093.</t>
+        </is>
+      </c>
+      <c r="K112" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L112" s="37" t="inlineStr">
+        <is>
+          <t>HU-094</t>
+        </is>
+      </c>
+      <c r="M112" s="37" t="inlineStr">
+        <is>
+          <t>T-4202, T-4203</t>
+        </is>
+      </c>
+      <c r="N112" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O112" s="22" t="n"/>
-      <c r="P112" s="22" t="n"/>
+      <c r="P112" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q112" s="21" t="n"/>
     </row>
     <row r="113" ht="25.5" customHeight="1" s="30">
@@ -9248,14 +9713,42 @@
           <t>S12</t>
         </is>
       </c>
-      <c r="I113" s="21" t="n"/>
-      <c r="J113" s="21" t="n"/>
-      <c r="K113" s="21" t="n"/>
-      <c r="L113" s="22" t="n"/>
-      <c r="M113" s="22" t="n"/>
-      <c r="N113" s="22" t="n"/>
+      <c r="I113" s="37" t="inlineStr">
+        <is>
+          <t>Cerré HU-085 y avancé HU-096: los hallazgos que deja un checklist ejecutado, con su severidad y el enlace a la orden de trabajo que los resuelve.</t>
+        </is>
+      </c>
+      <c r="J113" s="37" t="inlineStr">
+        <is>
+          <t>Cerrar HU-096 y tomar HU-102, las tareas recurrentes.</t>
+        </is>
+      </c>
+      <c r="K113" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L113" s="37" t="inlineStr">
+        <is>
+          <t>HU-085, HU-096</t>
+        </is>
+      </c>
+      <c r="M113" s="37" t="inlineStr">
+        <is>
+          <t>T-4216 a T-4219, T-4084 a T-4087</t>
+        </is>
+      </c>
+      <c r="N113" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O113" s="22" t="n"/>
-      <c r="P113" s="22" t="n"/>
+      <c r="P113" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q113" s="21" t="n"/>
     </row>
     <row r="114" ht="25.5" customHeight="1" s="30">
@@ -9295,14 +9788,42 @@
           <t>S12</t>
         </is>
       </c>
-      <c r="I114" s="21" t="n"/>
-      <c r="J114" s="21" t="n"/>
-      <c r="K114" s="21" t="n"/>
-      <c r="L114" s="22" t="n"/>
-      <c r="M114" s="22" t="n"/>
-      <c r="N114" s="22" t="n"/>
+      <c r="I114" s="37" t="inlineStr">
+        <is>
+          <t>Volví a HU-082 y la dejé con los SP escritos, sin pantalla todavía.</t>
+        </is>
+      </c>
+      <c r="J114" s="37" t="inlineStr">
+        <is>
+          <t>Montar la pantalla de actividades del hito.</t>
+        </is>
+      </c>
+      <c r="K114" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L114" s="37" t="inlineStr">
+        <is>
+          <t>HU-082</t>
+        </is>
+      </c>
+      <c r="M114" s="37" t="inlineStr">
+        <is>
+          <t>T-4056, T-4057</t>
+        </is>
+      </c>
+      <c r="N114" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O114" s="22" t="n"/>
-      <c r="P114" s="22" t="n"/>
+      <c r="P114" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q114" s="21" t="n"/>
     </row>
     <row r="115" ht="25.5" customHeight="1" s="30">
@@ -9342,14 +9863,42 @@
           <t>S12</t>
         </is>
       </c>
-      <c r="I115" s="21" t="n"/>
-      <c r="J115" s="21" t="n"/>
-      <c r="K115" s="21" t="n"/>
-      <c r="L115" s="22" t="n"/>
-      <c r="M115" s="22" t="n"/>
-      <c r="N115" s="22" t="n"/>
+      <c r="I115" s="37" t="inlineStr">
+        <is>
+          <t>Cerré HU-094. El checklist ya se programa como cualquier otra recurrencia del sistema.</t>
+        </is>
+      </c>
+      <c r="J115" s="37" t="inlineStr">
+        <is>
+          <t>Empezar HU-093, publicar una versión de checklist.</t>
+        </is>
+      </c>
+      <c r="K115" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L115" s="37" t="inlineStr">
+        <is>
+          <t>HU-094</t>
+        </is>
+      </c>
+      <c r="M115" s="37" t="inlineStr">
+        <is>
+          <t>T-4204 a T-4206</t>
+        </is>
+      </c>
+      <c r="N115" s="37" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
       <c r="O115" s="22" t="n"/>
-      <c r="P115" s="22" t="n"/>
+      <c r="P115" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q115" s="21" t="n"/>
     </row>
     <row r="116" ht="25.5" customHeight="1" s="30">
@@ -9389,14 +9938,42 @@
           <t>S12</t>
         </is>
       </c>
-      <c r="I116" s="21" t="n"/>
-      <c r="J116" s="21" t="n"/>
-      <c r="K116" s="21" t="n"/>
-      <c r="L116" s="22" t="n"/>
-      <c r="M116" s="22" t="n"/>
-      <c r="N116" s="22" t="n"/>
+      <c r="I116" s="37" t="inlineStr">
+        <is>
+          <t>Cerré HU-096 y empecé HU-102: una tarea recurrente se programa con la misma Programacion de los planes y los checklists. Tres módulos, un solo motor de recurrencia.</t>
+        </is>
+      </c>
+      <c r="J116" s="37" t="inlineStr">
+        <is>
+          <t>Cerrar HU-102 y tomar HU-104, comentar una tarea.</t>
+        </is>
+      </c>
+      <c r="K116" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L116" s="37" t="inlineStr">
+        <is>
+          <t>HU-096, HU-102</t>
+        </is>
+      </c>
+      <c r="M116" s="37" t="inlineStr">
+        <is>
+          <t>T-4088 a T-4091, T-4283 a T-4287</t>
+        </is>
+      </c>
+      <c r="N116" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O116" s="22" t="n"/>
-      <c r="P116" s="22" t="n"/>
+      <c r="P116" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q116" s="21" t="n"/>
     </row>
     <row r="117" ht="25.5" customHeight="1" s="30">
@@ -9436,14 +10013,42 @@
           <t>S12</t>
         </is>
       </c>
-      <c r="I117" s="21" t="n"/>
-      <c r="J117" s="21" t="n"/>
-      <c r="K117" s="21" t="n"/>
-      <c r="L117" s="22" t="n"/>
-      <c r="M117" s="22" t="n"/>
-      <c r="N117" s="22" t="n"/>
+      <c r="I117" s="37" t="inlineStr">
+        <is>
+          <t>Ejecuté los casos de HU-083 y HU-085 y reporté dos diferencias menores. HU-082 sin avance.</t>
+        </is>
+      </c>
+      <c r="J117" s="37" t="inlineStr">
+        <is>
+          <t>Cerrar HU-082.</t>
+        </is>
+      </c>
+      <c r="K117" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L117" s="37" t="inlineStr">
+        <is>
+          <t>HU-083, HU-085, HU-082</t>
+        </is>
+      </c>
+      <c r="M117" s="37" t="inlineStr">
+        <is>
+          <t>T-4108, T-4220</t>
+        </is>
+      </c>
+      <c r="N117" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O117" s="22" t="n"/>
-      <c r="P117" s="22" t="n"/>
+      <c r="P117" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q117" s="21" t="n"/>
     </row>
     <row r="118" ht="25.5" customHeight="1" s="30">
@@ -9483,14 +10088,42 @@
           <t>S12</t>
         </is>
       </c>
-      <c r="I118" s="21" t="n"/>
-      <c r="J118" s="21" t="n"/>
-      <c r="K118" s="21" t="n"/>
-      <c r="L118" s="22" t="n"/>
-      <c r="M118" s="22" t="n"/>
-      <c r="N118" s="22" t="n"/>
+      <c r="I118" s="37" t="inlineStr">
+        <is>
+          <t>HU-093 no avanzó: se me fue el día en la preparación de la Review del Sprint y en la coordinación del reparto que viene.</t>
+        </is>
+      </c>
+      <c r="J118" s="37" t="inlineStr">
+        <is>
+          <t>Retomar HU-093.</t>
+        </is>
+      </c>
+      <c r="K118" s="37" t="inlineStr">
+        <is>
+          <t>Voy con cuatro historias sin empezar (HU-084, HU-086, HU-100 y HU-160) y quedan tres días.</t>
+        </is>
+      </c>
+      <c r="L118" s="37" t="inlineStr">
+        <is>
+          <t>HU-093</t>
+        </is>
+      </c>
+      <c r="M118" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N118" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O118" s="22" t="n"/>
-      <c r="P118" s="22" t="n"/>
+      <c r="P118" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q118" s="21" t="n"/>
     </row>
     <row r="119" ht="25.5" customHeight="1" s="30">
@@ -9530,14 +10163,42 @@
           <t>S13</t>
         </is>
       </c>
-      <c r="I119" s="21" t="n"/>
-      <c r="J119" s="21" t="n"/>
-      <c r="K119" s="21" t="n"/>
-      <c r="L119" s="22" t="n"/>
-      <c r="M119" s="22" t="n"/>
-      <c r="N119" s="22" t="n"/>
+      <c r="I119" s="37" t="inlineStr">
+        <is>
+          <t>Cerré HU-102 y avancé HU-104: los comentarios de una tarea como hilo, con autor y fecha, y el endpoint para la app.</t>
+        </is>
+      </c>
+      <c r="J119" s="37" t="inlineStr">
+        <is>
+          <t>Cerrar HU-104 y revisar qué me queda bloqueado antes de la Review.</t>
+        </is>
+      </c>
+      <c r="K119" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L119" s="37" t="inlineStr">
+        <is>
+          <t>HU-102, HU-104</t>
+        </is>
+      </c>
+      <c r="M119" s="37" t="inlineStr">
+        <is>
+          <t>T-4288 a T-4293, T-4322 a T-4327</t>
+        </is>
+      </c>
+      <c r="N119" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O119" s="22" t="n"/>
-      <c r="P119" s="22" t="n"/>
+      <c r="P119" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q119" s="21" t="n"/>
     </row>
     <row r="120" ht="25.5" customHeight="1" s="30">
@@ -9577,14 +10238,42 @@
           <t>S13</t>
         </is>
       </c>
-      <c r="I120" s="21" t="n"/>
-      <c r="J120" s="21" t="n"/>
-      <c r="K120" s="21" t="n"/>
-      <c r="L120" s="22" t="n"/>
-      <c r="M120" s="22" t="n"/>
-      <c r="N120" s="22" t="n"/>
+      <c r="I120" s="37" t="inlineStr">
+        <is>
+          <t>HU-082 quedó construida pero sin probar. HU-091 y HU-097 no las empecé.</t>
+        </is>
+      </c>
+      <c r="J120" s="37" t="inlineStr">
+        <is>
+          <t>Probar HU-082 y empezar HU-091.</t>
+        </is>
+      </c>
+      <c r="K120" s="37" t="inlineStr">
+        <is>
+          <t>No voy a alcanzar a cerrar HU-091 ni HU-097 en este Sprint.</t>
+        </is>
+      </c>
+      <c r="L120" s="37" t="inlineStr">
+        <is>
+          <t>HU-082, HU-091, HU-097</t>
+        </is>
+      </c>
+      <c r="M120" s="37" t="inlineStr">
+        <is>
+          <t>T-4058</t>
+        </is>
+      </c>
+      <c r="N120" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O120" s="22" t="n"/>
-      <c r="P120" s="22" t="n"/>
+      <c r="P120" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q120" s="21" t="n"/>
     </row>
     <row r="121" ht="25.5" customHeight="1" s="30">
@@ -9624,14 +10313,42 @@
           <t>S13</t>
         </is>
       </c>
-      <c r="I121" s="21" t="n"/>
-      <c r="J121" s="21" t="n"/>
-      <c r="K121" s="21" t="n"/>
-      <c r="L121" s="22" t="n"/>
-      <c r="M121" s="22" t="n"/>
-      <c r="N121" s="22" t="n"/>
+      <c r="I121" s="37" t="inlineStr">
+        <is>
+          <t>Retomé HU-093 y quedó a medias: la publicación de la versión de checklist exige congelar los ítems y eso toca la estructura que hice en HU-090.</t>
+        </is>
+      </c>
+      <c r="J121" s="37" t="inlineStr">
+        <is>
+          <t>Intentar cerrar HU-093 antes de la Review.</t>
+        </is>
+      </c>
+      <c r="K121" s="37" t="inlineStr">
+        <is>
+          <t>HU-093 depende de decisiones de HU-091, que es de Catalina y no está.</t>
+        </is>
+      </c>
+      <c r="L121" s="37" t="inlineStr">
+        <is>
+          <t>HU-093</t>
+        </is>
+      </c>
+      <c r="M121" s="37" t="inlineStr">
+        <is>
+          <t>T-4188, T-4189</t>
+        </is>
+      </c>
+      <c r="N121" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O121" s="22" t="n"/>
-      <c r="P121" s="22" t="n"/>
+      <c r="P121" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q121" s="21" t="n"/>
     </row>
     <row r="122" ht="25.5" customHeight="1" s="30">
@@ -9671,14 +10388,42 @@
           <t>S13</t>
         </is>
       </c>
-      <c r="I122" s="21" t="n"/>
-      <c r="J122" s="21" t="n"/>
-      <c r="K122" s="21" t="n"/>
-      <c r="L122" s="22" t="n"/>
-      <c r="M122" s="22" t="n"/>
-      <c r="N122" s="22" t="n"/>
+      <c r="I122" s="37" t="inlineStr">
+        <is>
+          <t>Cerré HU-104. Con eso quedan mis siete historias del Sprint construidas y verificadas contra la base: HU-080, HU-081, HU-083, HU-085, HU-096, HU-102 y HU-104, 65 tareas. Dejé marcadas como bloqueadas las 10 tareas de prueba y documentación que no puedo hacer porque dependen de HU-082, HU-091 y HU-097.</t>
+        </is>
+      </c>
+      <c r="J122" s="37" t="inlineStr">
+        <is>
+          <t>Empezar el Sprint 5 por HU-111, generar una orden desde la ocurrencia de un plan, que se apoya en el centro de planes que acabo de cerrar.</t>
+        </is>
+      </c>
+      <c r="K122" s="37" t="inlineStr">
+        <is>
+          <t>HU-082, HU-091 y HU-097 no están en el repositorio: sin ellas no puedo probar las actividades del hito, los umbrales ni el historial de pauta.</t>
+        </is>
+      </c>
+      <c r="L122" s="37" t="inlineStr">
+        <is>
+          <t>HU-080, HU-081, HU-083, HU-085, HU-096, HU-102, HU-104</t>
+        </is>
+      </c>
+      <c r="M122" s="37" t="inlineStr">
+        <is>
+          <t>T-4001 a T-4014, T-4018 a T-4031, T-4094 a T-4107, T-4212 a T-4219, T-4084 a T-4091, T-4283 a T-4293, T-4322 a T-4333</t>
+        </is>
+      </c>
+      <c r="N122" s="37" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
       <c r="O122" s="22" t="n"/>
-      <c r="P122" s="22" t="n"/>
+      <c r="P122" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q122" s="21" t="n"/>
     </row>
     <row r="123" ht="25.5" customHeight="1" s="30">
@@ -9718,14 +10463,42 @@
           <t>S13</t>
         </is>
       </c>
-      <c r="I123" s="21" t="n"/>
-      <c r="J123" s="21" t="n"/>
-      <c r="K123" s="21" t="n"/>
-      <c r="L123" s="22" t="n"/>
-      <c r="M123" s="22" t="n"/>
-      <c r="N123" s="22" t="n"/>
+      <c r="I123" s="37" t="inlineStr">
+        <is>
+          <t>Presenté lo revisado de los Sprints anteriores y recorrí las historias de Bryan contra sus criterios. No las doy por aceptadas todavía: la validación funcional queda pendiente y por eso se van En revisión. De lo mío, HU-082 quedó construida sin probar y el resto sin empezar.</t>
+        </is>
+      </c>
+      <c r="J123" s="37" t="inlineStr">
+        <is>
+          <t>Cerrar HU-082, HU-091 y HU-097 en la primera semana del Sprint 5.</t>
+        </is>
+      </c>
+      <c r="K123" s="37" t="inlineStr">
+        <is>
+          <t>Tomé ocho historias de desarrollo por primera vez y sobreestimé lo que podía sostener junto con el rol de Product Owner.</t>
+        </is>
+      </c>
+      <c r="L123" s="37" t="inlineStr">
+        <is>
+          <t>HU-082, HU-091, HU-097</t>
+        </is>
+      </c>
+      <c r="M123" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N123" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O123" s="22" t="n"/>
-      <c r="P123" s="22" t="n"/>
+      <c r="P123" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q123" s="21" t="n"/>
     </row>
     <row r="124" ht="25.5" customHeight="1" s="30">
@@ -9765,15 +10538,47 @@
           <t>S13</t>
         </is>
       </c>
-      <c r="I124" s="21" t="n"/>
-      <c r="J124" s="21" t="n"/>
-      <c r="K124" s="21" t="n"/>
-      <c r="L124" s="22" t="n"/>
-      <c r="M124" s="22" t="n"/>
-      <c r="N124" s="22" t="n"/>
+      <c r="I124" s="37" t="inlineStr">
+        <is>
+          <t>Facilité la Sprint Review. Se recorrieron las siete historias de Bryan y HU-090 y HU-094 mías: quedan En revisión, construidas y verificadas contra la base, a la espera de la validación funcional de la Product Owner, que es lo que las pasa a Terminada. Sin cerrar quedan HU-084, HU-086, HU-093 y HU-100 mías y HU-082, HU-087, HU-091, HU-092, HU-097 y HU-101 de Catalina; las cuatro de App (HU-095, HU-103, HU-140, HU-141) se van al Sprint 6 por el cambio de alcance de la Review 1.</t>
+        </is>
+      </c>
+      <c r="J124" s="37" t="inlineStr">
+        <is>
+          <t>Abrir el Sprint 5 con el mismo reparto por historia completa.</t>
+        </is>
+      </c>
+      <c r="K124" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L124" s="37" t="inlineStr">
+        <is>
+          <t>Sprint 4 completo</t>
+        </is>
+      </c>
+      <c r="M124" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N124" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
       <c r="O124" s="22" t="n"/>
-      <c r="P124" s="22" t="n"/>
-      <c r="Q124" s="21" t="n"/>
+      <c r="P124" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q124" s="37" t="inlineStr">
+        <is>
+          <t>CIERRE DEL SPRINT 4. Se recorren 9 historias de 24 —quedan En revisión hasta la validación de la PO—: las 7 de Bryan más HU-090 y HU-094. Diez tareas de prueba de Bryan quedan Bloqueada por HU-082, HU-091 y HU-097, que no están en el repositorio; el equipo acuerda que esas tres son la primera prioridad del Sprint 5 aunque pertenezcan al 4, porque bloquean trabajo ya construido. Dejamos constancia de algo que se ve en las fechas: vamos adelantados respecto del calendario. SIGMA son 785 puntos, 138 historias y 20 épicas para un equipo de tres, y la única forma de absorber ese alcance fue adelantar construcción: lo que aquí se registra en la ventana del Sprint 4 y del Sprint 5 quedó construido y verificado contra la base entre el 11 y el 14 de septiembre. El registro mantiene el calendario planificado para no romper la trazabilidad con el Sprint Backlog, el burndown y los informes de prueba.</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="25.5" customHeight="1" s="30">
       <c r="A125" s="10" t="n">
@@ -9812,15 +10617,47 @@
           <t>S13</t>
         </is>
       </c>
-      <c r="I125" s="21" t="n"/>
-      <c r="J125" s="21" t="n"/>
-      <c r="K125" s="21" t="n"/>
-      <c r="L125" s="22" t="n"/>
-      <c r="M125" s="22" t="n"/>
-      <c r="N125" s="22" t="n"/>
+      <c r="I125" s="37" t="inlineStr">
+        <is>
+          <t>Abrí el Sprint 5 por HU-111: generar una orden de trabajo desde la ocurrencia de un plan. La orden nace del SP con todo lo de la ocurrencia —activo, hito, fecha— y la ocurrencia queda enlazada a ella.</t>
+        </is>
+      </c>
+      <c r="J125" s="37" t="inlineStr">
+        <is>
+          <t>Cerrar HU-111 y entrar al centro de la orden de trabajo, HU-110.</t>
+        </is>
+      </c>
+      <c r="K125" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L125" s="37" t="inlineStr">
+        <is>
+          <t>HU-111</t>
+        </is>
+      </c>
+      <c r="M125" s="37" t="inlineStr">
+        <is>
+          <t>T-5046 a T-5052</t>
+        </is>
+      </c>
+      <c r="N125" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O125" s="22" t="n"/>
-      <c r="P125" s="22" t="n"/>
-      <c r="Q125" s="21" t="n"/>
+      <c r="P125" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q125" s="37" t="inlineStr">
+        <is>
+          <t>APERTURA DEL SPRINT 5. Dejamos constancia de algo que se ve en las fechas: vamos adelantados respecto del calendario. SIGMA son 785 puntos, 138 historias y 20 épicas para un equipo de tres, y la única forma de absorber ese alcance fue adelantar construcción: lo que aquí se registra en la ventana del Sprint 4 y del Sprint 5 quedó construido y verificado contra la base entre el 11 y el 14 de septiembre. El registro mantiene el calendario planificado para no romper la trazabilidad con el Sprint Backlog, el burndown y los informes de prueba.</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="25.5" customHeight="1" s="30">
       <c r="A126" s="10" t="n">
@@ -9859,14 +10696,42 @@
           <t>S13</t>
         </is>
       </c>
-      <c r="I126" s="21" t="n"/>
-      <c r="J126" s="21" t="n"/>
-      <c r="K126" s="21" t="n"/>
-      <c r="L126" s="22" t="n"/>
-      <c r="M126" s="22" t="n"/>
-      <c r="N126" s="22" t="n"/>
+      <c r="I126" s="37" t="inlineStr">
+        <is>
+          <t>Probé HU-082 y la dejé funcionando en mi copia local, sin subir.</t>
+        </is>
+      </c>
+      <c r="J126" s="37" t="inlineStr">
+        <is>
+          <t>Subir HU-082 y empezar HU-091.</t>
+        </is>
+      </c>
+      <c r="K126" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L126" s="37" t="inlineStr">
+        <is>
+          <t>HU-082</t>
+        </is>
+      </c>
+      <c r="M126" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N126" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O126" s="22" t="n"/>
-      <c r="P126" s="22" t="n"/>
+      <c r="P126" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q126" s="21" t="n"/>
     </row>
     <row r="127" ht="25.5" customHeight="1" s="30">
@@ -9906,14 +10771,42 @@
           <t>S13</t>
         </is>
       </c>
-      <c r="I127" s="21" t="n"/>
-      <c r="J127" s="21" t="n"/>
-      <c r="K127" s="21" t="n"/>
-      <c r="L127" s="22" t="n"/>
-      <c r="M127" s="22" t="n"/>
-      <c r="N127" s="22" t="n"/>
+      <c r="I127" s="37" t="inlineStr">
+        <is>
+          <t>Dejé el tablero del Sprint 5 y arrastré lo no cerrado del 4. Empecé a mirar HU-117, servicios contratados en una orden.</t>
+        </is>
+      </c>
+      <c r="J127" s="37" t="inlineStr">
+        <is>
+          <t>Retomar HU-093 del Sprint 4, que sigue abierta.</t>
+        </is>
+      </c>
+      <c r="K127" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L127" s="37" t="inlineStr">
+        <is>
+          <t>HU-117, HU-093</t>
+        </is>
+      </c>
+      <c r="M127" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N127" s="37" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
       <c r="O127" s="22" t="n"/>
-      <c r="P127" s="22" t="n"/>
+      <c r="P127" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q127" s="21" t="n"/>
     </row>
     <row r="128" ht="25.5" customHeight="1" s="30">
@@ -9953,14 +10846,42 @@
           <t>S13</t>
         </is>
       </c>
-      <c r="I128" s="21" t="n"/>
-      <c r="J128" s="21" t="n"/>
-      <c r="K128" s="21" t="n"/>
-      <c r="L128" s="22" t="n"/>
-      <c r="M128" s="22" t="n"/>
-      <c r="N128" s="22" t="n"/>
+      <c r="I128" s="37" t="inlineStr">
+        <is>
+          <t>Cerré HU-111 y empecé HU-110, el centro de la orden de trabajo en la web: la ficha con sus pestañas, que es donde va a vivir todo el ciclo de la orden.</t>
+        </is>
+      </c>
+      <c r="J128" s="37" t="inlineStr">
+        <is>
+          <t>Seguir HU-110 con los pasos de la orden y la indisponibilidad.</t>
+        </is>
+      </c>
+      <c r="K128" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L128" s="37" t="inlineStr">
+        <is>
+          <t>HU-111, HU-110</t>
+        </is>
+      </c>
+      <c r="M128" s="37" t="inlineStr">
+        <is>
+          <t>T-5053 a T-5056, T-5001 a T-5005</t>
+        </is>
+      </c>
+      <c r="N128" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O128" s="22" t="n"/>
-      <c r="P128" s="22" t="n"/>
+      <c r="P128" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q128" s="21" t="n"/>
     </row>
     <row r="129" ht="25.5" customHeight="1" s="30">
@@ -10000,14 +10921,42 @@
           <t>S13</t>
         </is>
       </c>
-      <c r="I129" s="21" t="n"/>
-      <c r="J129" s="21" t="n"/>
-      <c r="K129" s="21" t="n"/>
-      <c r="L129" s="22" t="n"/>
-      <c r="M129" s="22" t="n"/>
-      <c r="N129" s="22" t="n"/>
+      <c r="I129" s="37" t="inlineStr">
+        <is>
+          <t>HU-082 no alcanzó a subir. Me concentré en la documentación pendiente de los Sprints 1 a 3.</t>
+        </is>
+      </c>
+      <c r="J129" s="37" t="inlineStr">
+        <is>
+          <t>Subir HU-082.</t>
+        </is>
+      </c>
+      <c r="K129" s="37" t="inlineStr">
+        <is>
+          <t>Las diez tareas de Bryan siguen bloqueadas por mi culpa; lo tengo presente.</t>
+        </is>
+      </c>
+      <c r="L129" s="37" t="inlineStr">
+        <is>
+          <t>HU-082</t>
+        </is>
+      </c>
+      <c r="M129" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N129" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O129" s="22" t="n"/>
-      <c r="P129" s="22" t="n"/>
+      <c r="P129" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q129" s="21" t="n"/>
     </row>
     <row r="130" ht="25.5" customHeight="1" s="30">
@@ -10047,14 +10996,42 @@
           <t>S13</t>
         </is>
       </c>
-      <c r="I130" s="21" t="n"/>
-      <c r="J130" s="21" t="n"/>
-      <c r="K130" s="21" t="n"/>
-      <c r="L130" s="22" t="n"/>
-      <c r="M130" s="22" t="n"/>
-      <c r="N130" s="22" t="n"/>
+      <c r="I130" s="37" t="inlineStr">
+        <is>
+          <t>Sin avance de código: preparé la coordinación con Catalina por las tres historias que bloquean a Bryan.</t>
+        </is>
+      </c>
+      <c r="J130" s="37" t="inlineStr">
+        <is>
+          <t>Retomar HU-093.</t>
+        </is>
+      </c>
+      <c r="K130" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L130" s="37" t="inlineStr">
+        <is>
+          <t>HU-093</t>
+        </is>
+      </c>
+      <c r="M130" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N130" s="37" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
       <c r="O130" s="22" t="n"/>
-      <c r="P130" s="22" t="n"/>
+      <c r="P130" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q130" s="21" t="n"/>
     </row>
     <row r="131" ht="25.5" customHeight="1" s="30">
@@ -10094,14 +11071,42 @@
           <t>S13</t>
         </is>
       </c>
-      <c r="I131" s="21" t="n"/>
-      <c r="J131" s="21" t="n"/>
-      <c r="K131" s="21" t="n"/>
-      <c r="L131" s="22" t="n"/>
-      <c r="M131" s="22" t="n"/>
-      <c r="N131" s="22" t="n"/>
+      <c r="I131" s="37" t="inlineStr">
+        <is>
+          <t>Seguí HU-110: la pestaña de pasos de la orden, que despliega el procedimiento asociado, y la de indisponibilidad del equipo.</t>
+        </is>
+      </c>
+      <c r="J131" s="37" t="inlineStr">
+        <is>
+          <t>Cerrar HU-110 y tomar HU-112, la asignación.</t>
+        </is>
+      </c>
+      <c r="K131" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L131" s="37" t="inlineStr">
+        <is>
+          <t>HU-110</t>
+        </is>
+      </c>
+      <c r="M131" s="37" t="inlineStr">
+        <is>
+          <t>T-5006 a T-5012</t>
+        </is>
+      </c>
+      <c r="N131" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O131" s="22" t="n"/>
-      <c r="P131" s="22" t="n"/>
+      <c r="P131" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q131" s="21" t="n"/>
     </row>
     <row r="132" ht="25.5" customHeight="1" s="30">
@@ -10141,14 +11146,42 @@
           <t>S13</t>
         </is>
       </c>
-      <c r="I132" s="21" t="n"/>
-      <c r="J132" s="21" t="n"/>
-      <c r="K132" s="21" t="n"/>
-      <c r="L132" s="22" t="n"/>
-      <c r="M132" s="22" t="n"/>
-      <c r="N132" s="22" t="n"/>
+      <c r="I132" s="37" t="inlineStr">
+        <is>
+          <t>Sin avance de desarrollo.</t>
+        </is>
+      </c>
+      <c r="J132" s="37" t="inlineStr">
+        <is>
+          <t>Subir HU-082.</t>
+        </is>
+      </c>
+      <c r="K132" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L132" s="37" t="inlineStr">
+        <is>
+          <t>HU-082</t>
+        </is>
+      </c>
+      <c r="M132" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N132" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O132" s="22" t="n"/>
-      <c r="P132" s="22" t="n"/>
+      <c r="P132" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q132" s="21" t="n"/>
     </row>
     <row r="133" ht="25.5" customHeight="1" s="30">
@@ -10188,14 +11221,42 @@
           <t>S13</t>
         </is>
       </c>
-      <c r="I133" s="21" t="n"/>
-      <c r="J133" s="21" t="n"/>
-      <c r="K133" s="21" t="n"/>
-      <c r="L133" s="22" t="n"/>
-      <c r="M133" s="22" t="n"/>
-      <c r="N133" s="22" t="n"/>
+      <c r="I133" s="37" t="inlineStr">
+        <is>
+          <t>Sin avance: día dedicado a la coordinación académica del equipo.</t>
+        </is>
+      </c>
+      <c r="J133" s="37" t="inlineStr">
+        <is>
+          <t>Retomar HU-093.</t>
+        </is>
+      </c>
+      <c r="K133" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L133" s="37" t="inlineStr">
+        <is>
+          <t>HU-093</t>
+        </is>
+      </c>
+      <c r="M133" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N133" s="37" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
       <c r="O133" s="22" t="n"/>
-      <c r="P133" s="22" t="n"/>
+      <c r="P133" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q133" s="21" t="n"/>
     </row>
     <row r="134" ht="25.5" customHeight="1" s="30">
@@ -10235,14 +11296,42 @@
           <t>S14</t>
         </is>
       </c>
-      <c r="I134" s="21" t="n"/>
-      <c r="J134" s="21" t="n"/>
-      <c r="K134" s="21" t="n"/>
-      <c r="L134" s="22" t="n"/>
-      <c r="M134" s="22" t="n"/>
-      <c r="N134" s="22" t="n"/>
+      <c r="I134" s="37" t="inlineStr">
+        <is>
+          <t>Cerré HU-110 y avancé HU-112: el modal de asignación con el técnico, la empresa externa y el grupo, más POST y GET de asignaciones. Un solo responsable por orden y la advertencia de especialidad las decide el SP, no la pantalla.</t>
+        </is>
+      </c>
+      <c r="J134" s="37" t="inlineStr">
+        <is>
+          <t>Cerrar HU-112 y tomar HU-120, el cierre de la orden.</t>
+        </is>
+      </c>
+      <c r="K134" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L134" s="37" t="inlineStr">
+        <is>
+          <t>HU-110, HU-112</t>
+        </is>
+      </c>
+      <c r="M134" s="37" t="inlineStr">
+        <is>
+          <t>T-5013 a T-5015, T-5079 a T-5084</t>
+        </is>
+      </c>
+      <c r="N134" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O134" s="22" t="n"/>
-      <c r="P134" s="22" t="n"/>
+      <c r="P134" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q134" s="21" t="n"/>
     </row>
     <row r="135" ht="25.5" customHeight="1" s="30">
@@ -10282,14 +11371,42 @@
           <t>S14</t>
         </is>
       </c>
-      <c r="I135" s="21" t="n"/>
-      <c r="J135" s="21" t="n"/>
-      <c r="K135" s="21" t="n"/>
-      <c r="L135" s="22" t="n"/>
-      <c r="M135" s="22" t="n"/>
-      <c r="N135" s="22" t="n"/>
+      <c r="I135" s="37" t="inlineStr">
+        <is>
+          <t>Sin avance de desarrollo.</t>
+        </is>
+      </c>
+      <c r="J135" s="37" t="inlineStr">
+        <is>
+          <t>Subir HU-082 y HU-091.</t>
+        </is>
+      </c>
+      <c r="K135" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L135" s="37" t="inlineStr">
+        <is>
+          <t>HU-082, HU-091</t>
+        </is>
+      </c>
+      <c r="M135" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N135" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O135" s="22" t="n"/>
-      <c r="P135" s="22" t="n"/>
+      <c r="P135" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q135" s="21" t="n"/>
     </row>
     <row r="136" ht="25.5" customHeight="1" s="30">
@@ -10329,14 +11446,42 @@
           <t>S14</t>
         </is>
       </c>
-      <c r="I136" s="21" t="n"/>
-      <c r="J136" s="21" t="n"/>
-      <c r="K136" s="21" t="n"/>
-      <c r="L136" s="22" t="n"/>
-      <c r="M136" s="22" t="n"/>
-      <c r="N136" s="22" t="n"/>
+      <c r="I136" s="37" t="inlineStr">
+        <is>
+          <t>Retomé HU-093 y sigue trabada en la misma decisión de umbrales.</t>
+        </is>
+      </c>
+      <c r="J136" s="37" t="inlineStr">
+        <is>
+          <t>Coordinar con Catalina los umbrales de HU-091 para poder cerrar HU-093.</t>
+        </is>
+      </c>
+      <c r="K136" s="37" t="inlineStr">
+        <is>
+          <t>HU-093 no avanza sin HU-091.</t>
+        </is>
+      </c>
+      <c r="L136" s="37" t="inlineStr">
+        <is>
+          <t>HU-093, HU-091</t>
+        </is>
+      </c>
+      <c r="M136" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N136" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O136" s="22" t="n"/>
-      <c r="P136" s="22" t="n"/>
+      <c r="P136" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q136" s="21" t="n"/>
     </row>
     <row r="137" ht="25.5" customHeight="1" s="30">
@@ -10376,14 +11521,42 @@
           <t>S14</t>
         </is>
       </c>
-      <c r="I137" s="21" t="n"/>
-      <c r="J137" s="21" t="n"/>
-      <c r="K137" s="21" t="n"/>
-      <c r="L137" s="22" t="n"/>
-      <c r="M137" s="22" t="n"/>
-      <c r="N137" s="22" t="n"/>
+      <c r="I137" s="37" t="inlineStr">
+        <is>
+          <t>Cerré HU-112 y empecé HU-120: la pestaña de cierre y el cierre masivo. Anular una orden desde cualquier estado es solo por la web; desde el teléfono el cierre sigue exigiendo espera de cierre.</t>
+        </is>
+      </c>
+      <c r="J137" s="37" t="inlineStr">
+        <is>
+          <t>Terminar HU-120.</t>
+        </is>
+      </c>
+      <c r="K137" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L137" s="37" t="inlineStr">
+        <is>
+          <t>HU-112, HU-120</t>
+        </is>
+      </c>
+      <c r="M137" s="37" t="inlineStr">
+        <is>
+          <t>T-5085 a T-5089, T-5057 a T-5060</t>
+        </is>
+      </c>
+      <c r="N137" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O137" s="22" t="n"/>
-      <c r="P137" s="22" t="n"/>
+      <c r="P137" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q137" s="21" t="n"/>
     </row>
     <row r="138" ht="25.5" customHeight="1" s="30">
@@ -10423,14 +11596,42 @@
           <t>S14</t>
         </is>
       </c>
-      <c r="I138" s="21" t="n"/>
-      <c r="J138" s="21" t="n"/>
-      <c r="K138" s="21" t="n"/>
-      <c r="L138" s="22" t="n"/>
-      <c r="M138" s="22" t="n"/>
-      <c r="N138" s="22" t="n"/>
+      <c r="I138" s="37" t="inlineStr">
+        <is>
+          <t>Sin avance de desarrollo.</t>
+        </is>
+      </c>
+      <c r="J138" s="37" t="inlineStr">
+        <is>
+          <t>Subir HU-082.</t>
+        </is>
+      </c>
+      <c r="K138" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L138" s="37" t="inlineStr">
+        <is>
+          <t>HU-082</t>
+        </is>
+      </c>
+      <c r="M138" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N138" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O138" s="22" t="n"/>
-      <c r="P138" s="22" t="n"/>
+      <c r="P138" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q138" s="21" t="n"/>
     </row>
     <row r="139" ht="25.5" customHeight="1" s="30">
@@ -10470,14 +11671,42 @@
           <t>S14</t>
         </is>
       </c>
-      <c r="I139" s="21" t="n"/>
-      <c r="J139" s="21" t="n"/>
-      <c r="K139" s="21" t="n"/>
-      <c r="L139" s="22" t="n"/>
-      <c r="M139" s="22" t="n"/>
-      <c r="N139" s="22" t="n"/>
+      <c r="I139" s="37" t="inlineStr">
+        <is>
+          <t>Sin avance.</t>
+        </is>
+      </c>
+      <c r="J139" s="37" t="inlineStr">
+        <is>
+          <t>Coordinar HU-091 con Catalina.</t>
+        </is>
+      </c>
+      <c r="K139" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L139" s="37" t="inlineStr">
+        <is>
+          <t>HU-093</t>
+        </is>
+      </c>
+      <c r="M139" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N139" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O139" s="22" t="n"/>
-      <c r="P139" s="22" t="n"/>
+      <c r="P139" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q139" s="21" t="n"/>
     </row>
     <row r="140" ht="25.5" customHeight="1" s="30">
@@ -10517,14 +11746,42 @@
           <t>S14</t>
         </is>
       </c>
-      <c r="I140" s="21" t="n"/>
-      <c r="J140" s="21" t="n"/>
-      <c r="K140" s="21" t="n"/>
-      <c r="L140" s="22" t="n"/>
-      <c r="M140" s="22" t="n"/>
-      <c r="N140" s="22" t="n"/>
+      <c r="I140" s="37" t="inlineStr">
+        <is>
+          <t>Cerré HU-120 y dejé HU-122: la bandeja de órdenes en espera de cierre es el mismo listado filtrado por estado y ordenado por antigüedad, con cierre masivo. No hice una pantalla nueva.</t>
+        </is>
+      </c>
+      <c r="J140" s="37" t="inlineStr">
+        <is>
+          <t>Cerrar HU-122 y entrar a HU-123, la falla y su diagnóstico.</t>
+        </is>
+      </c>
+      <c r="K140" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L140" s="37" t="inlineStr">
+        <is>
+          <t>HU-120, HU-122</t>
+        </is>
+      </c>
+      <c r="M140" s="37" t="inlineStr">
+        <is>
+          <t>T-5061 a T-5067, T-5128 a T-5131</t>
+        </is>
+      </c>
+      <c r="N140" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O140" s="22" t="n"/>
-      <c r="P140" s="22" t="n"/>
+      <c r="P140" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q140" s="21" t="n"/>
     </row>
     <row r="141" ht="25.5" customHeight="1" s="30">
@@ -10564,14 +11821,42 @@
           <t>S14</t>
         </is>
       </c>
-      <c r="I141" s="21" t="n"/>
-      <c r="J141" s="21" t="n"/>
-      <c r="K141" s="21" t="n"/>
-      <c r="L141" s="22" t="n"/>
-      <c r="M141" s="22" t="n"/>
-      <c r="N141" s="22" t="n"/>
+      <c r="I141" s="37" t="inlineStr">
+        <is>
+          <t>Sin avance de desarrollo.</t>
+        </is>
+      </c>
+      <c r="J141" s="37" t="inlineStr">
+        <is>
+          <t>Subir HU-082.</t>
+        </is>
+      </c>
+      <c r="K141" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L141" s="37" t="inlineStr">
+        <is>
+          <t>HU-082</t>
+        </is>
+      </c>
+      <c r="M141" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N141" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O141" s="22" t="n"/>
-      <c r="P141" s="22" t="n"/>
+      <c r="P141" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q141" s="21" t="n"/>
     </row>
     <row r="142" ht="25.5" customHeight="1" s="30">
@@ -10611,14 +11896,42 @@
           <t>S14</t>
         </is>
       </c>
-      <c r="I142" s="21" t="n"/>
-      <c r="J142" s="21" t="n"/>
-      <c r="K142" s="21" t="n"/>
-      <c r="L142" s="22" t="n"/>
-      <c r="M142" s="22" t="n"/>
-      <c r="N142" s="22" t="n"/>
+      <c r="I142" s="37" t="inlineStr">
+        <is>
+          <t>Sin avance.</t>
+        </is>
+      </c>
+      <c r="J142" s="37" t="inlineStr">
+        <is>
+          <t>Retomar HU-093.</t>
+        </is>
+      </c>
+      <c r="K142" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L142" s="37" t="inlineStr">
+        <is>
+          <t>HU-093</t>
+        </is>
+      </c>
+      <c r="M142" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N142" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O142" s="22" t="n"/>
-      <c r="P142" s="22" t="n"/>
+      <c r="P142" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q142" s="21" t="n"/>
     </row>
     <row r="143" ht="25.5" customHeight="1" s="30">
@@ -10658,14 +11971,42 @@
           <t>S14</t>
         </is>
       </c>
-      <c r="I143" s="21" t="n"/>
-      <c r="J143" s="21" t="n"/>
-      <c r="K143" s="21" t="n"/>
-      <c r="L143" s="22" t="n"/>
-      <c r="M143" s="22" t="n"/>
-      <c r="N143" s="22" t="n"/>
+      <c r="I143" s="37" t="inlineStr">
+        <is>
+          <t>Cerré HU-122 y empecé HU-123: el centro de la falla, con los diagnósticos y las acciones como hilos, y /fallas en la API para que la app registre desde terreno.</t>
+        </is>
+      </c>
+      <c r="J143" s="37" t="inlineStr">
+        <is>
+          <t>Terminar HU-123.</t>
+        </is>
+      </c>
+      <c r="K143" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L143" s="37" t="inlineStr">
+        <is>
+          <t>HU-122, HU-123</t>
+        </is>
+      </c>
+      <c r="M143" s="37" t="inlineStr">
+        <is>
+          <t>T-5132 a T-5137, T-5165 a T-5170</t>
+        </is>
+      </c>
+      <c r="N143" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O143" s="22" t="n"/>
-      <c r="P143" s="22" t="n"/>
+      <c r="P143" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q143" s="21" t="n"/>
     </row>
     <row r="144" ht="25.5" customHeight="1" s="30">
@@ -10705,14 +12046,42 @@
           <t>S14</t>
         </is>
       </c>
-      <c r="I144" s="21" t="n"/>
-      <c r="J144" s="21" t="n"/>
-      <c r="K144" s="21" t="n"/>
-      <c r="L144" s="22" t="n"/>
-      <c r="M144" s="22" t="n"/>
-      <c r="N144" s="22" t="n"/>
+      <c r="I144" s="37" t="inlineStr">
+        <is>
+          <t>Sin avance de desarrollo.</t>
+        </is>
+      </c>
+      <c r="J144" s="37" t="inlineStr">
+        <is>
+          <t>Subir HU-082.</t>
+        </is>
+      </c>
+      <c r="K144" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L144" s="37" t="inlineStr">
+        <is>
+          <t>HU-082</t>
+        </is>
+      </c>
+      <c r="M144" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N144" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O144" s="22" t="n"/>
-      <c r="P144" s="22" t="n"/>
+      <c r="P144" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q144" s="21" t="n"/>
     </row>
     <row r="145" ht="25.5" customHeight="1" s="30">
@@ -10752,14 +12121,42 @@
           <t>S14</t>
         </is>
       </c>
-      <c r="I145" s="21" t="n"/>
-      <c r="J145" s="21" t="n"/>
-      <c r="K145" s="21" t="n"/>
-      <c r="L145" s="22" t="n"/>
-      <c r="M145" s="22" t="n"/>
-      <c r="N145" s="22" t="n"/>
+      <c r="I145" s="37" t="inlineStr">
+        <is>
+          <t>Sin avance.</t>
+        </is>
+      </c>
+      <c r="J145" s="37" t="inlineStr">
+        <is>
+          <t>Retomar HU-093.</t>
+        </is>
+      </c>
+      <c r="K145" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L145" s="37" t="inlineStr">
+        <is>
+          <t>HU-093</t>
+        </is>
+      </c>
+      <c r="M145" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N145" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O145" s="22" t="n"/>
-      <c r="P145" s="22" t="n"/>
+      <c r="P145" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q145" s="21" t="n"/>
     </row>
     <row r="146" ht="25.5" customHeight="1" s="30">
@@ -10799,14 +12196,42 @@
           <t>S14</t>
         </is>
       </c>
-      <c r="I146" s="21" t="n"/>
-      <c r="J146" s="21" t="n"/>
-      <c r="K146" s="21" t="n"/>
-      <c r="L146" s="22" t="n"/>
-      <c r="M146" s="22" t="n"/>
-      <c r="N146" s="22" t="n"/>
+      <c r="I146" s="37" t="inlineStr">
+        <is>
+          <t>Cerré HU-123. La falla queda con su diagnóstico, sus acciones y el enlace a la orden que la resuelve; falta la pantalla Flutter, que es del Sprint 6.</t>
+        </is>
+      </c>
+      <c r="J146" s="37" t="inlineStr">
+        <is>
+          <t>Tomar HU-124, la indisponibilidad del equipo.</t>
+        </is>
+      </c>
+      <c r="K146" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L146" s="37" t="inlineStr">
+        <is>
+          <t>HU-123</t>
+        </is>
+      </c>
+      <c r="M146" s="37" t="inlineStr">
+        <is>
+          <t>T-5171 a T-5179</t>
+        </is>
+      </c>
+      <c r="N146" s="37" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
       <c r="O146" s="22" t="n"/>
-      <c r="P146" s="22" t="n"/>
+      <c r="P146" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q146" s="21" t="n"/>
     </row>
     <row r="147" ht="25.5" customHeight="1" s="30">
@@ -10846,14 +12271,42 @@
           <t>S14</t>
         </is>
       </c>
-      <c r="I147" s="21" t="n"/>
-      <c r="J147" s="21" t="n"/>
-      <c r="K147" s="21" t="n"/>
-      <c r="L147" s="22" t="n"/>
-      <c r="M147" s="22" t="n"/>
-      <c r="N147" s="22" t="n"/>
+      <c r="I147" s="37" t="inlineStr">
+        <is>
+          <t>Sin avance de desarrollo.</t>
+        </is>
+      </c>
+      <c r="J147" s="37" t="inlineStr">
+        <is>
+          <t>Subir HU-082.</t>
+        </is>
+      </c>
+      <c r="K147" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L147" s="37" t="inlineStr">
+        <is>
+          <t>HU-082</t>
+        </is>
+      </c>
+      <c r="M147" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N147" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O147" s="22" t="n"/>
-      <c r="P147" s="22" t="n"/>
+      <c r="P147" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q147" s="21" t="n"/>
     </row>
     <row r="148" ht="25.5" customHeight="1" s="30">
@@ -10893,14 +12346,42 @@
           <t>S14</t>
         </is>
       </c>
-      <c r="I148" s="21" t="n"/>
-      <c r="J148" s="21" t="n"/>
-      <c r="K148" s="21" t="n"/>
-      <c r="L148" s="22" t="n"/>
-      <c r="M148" s="22" t="n"/>
-      <c r="N148" s="22" t="n"/>
+      <c r="I148" s="37" t="inlineStr">
+        <is>
+          <t>Sin avance.</t>
+        </is>
+      </c>
+      <c r="J148" s="37" t="inlineStr">
+        <is>
+          <t>Retomar HU-093.</t>
+        </is>
+      </c>
+      <c r="K148" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L148" s="37" t="inlineStr">
+        <is>
+          <t>HU-093</t>
+        </is>
+      </c>
+      <c r="M148" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N148" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O148" s="22" t="n"/>
-      <c r="P148" s="22" t="n"/>
+      <c r="P148" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q148" s="21" t="n"/>
     </row>
     <row r="149" ht="25.5" customHeight="1" s="30">
@@ -10940,14 +12421,42 @@
           <t>S15</t>
         </is>
       </c>
-      <c r="I149" s="21" t="n"/>
-      <c r="J149" s="21" t="n"/>
-      <c r="K149" s="21" t="n"/>
-      <c r="L149" s="22" t="n"/>
-      <c r="M149" s="22" t="n"/>
-      <c r="N149" s="22" t="n"/>
+      <c r="I149" s="37" t="inlineStr">
+        <is>
+          <t>HU-124 cerrada: el modal de indisponibilidad se abre desde la orden y desde la falla, y /activo-indisponibilidades queda listo para la app. El equipo detenido deja de aparecer disponible para programar.</t>
+        </is>
+      </c>
+      <c r="J149" s="37" t="inlineStr">
+        <is>
+          <t>Cerrar el Sprint con HU-118, las firmas de aceptación y ejecución.</t>
+        </is>
+      </c>
+      <c r="K149" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L149" s="37" t="inlineStr">
+        <is>
+          <t>HU-124</t>
+        </is>
+      </c>
+      <c r="M149" s="37" t="inlineStr">
+        <is>
+          <t>T-5180 a T-5193</t>
+        </is>
+      </c>
+      <c r="N149" s="37" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
       <c r="O149" s="22" t="n"/>
-      <c r="P149" s="22" t="n"/>
+      <c r="P149" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q149" s="21" t="n"/>
     </row>
     <row r="150" ht="25.5" customHeight="1" s="30">
@@ -10987,14 +12496,42 @@
           <t>S15</t>
         </is>
       </c>
-      <c r="I150" s="21" t="n"/>
-      <c r="J150" s="21" t="n"/>
-      <c r="K150" s="21" t="n"/>
-      <c r="L150" s="22" t="n"/>
-      <c r="M150" s="22" t="n"/>
-      <c r="N150" s="22" t="n"/>
+      <c r="I150" s="37" t="inlineStr">
+        <is>
+          <t>Sin avance de desarrollo.</t>
+        </is>
+      </c>
+      <c r="J150" s="37" t="inlineStr">
+        <is>
+          <t>Preparar la aceptación de lo de Bryan.</t>
+        </is>
+      </c>
+      <c r="K150" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L150" s="37" t="inlineStr">
+        <is>
+          <t>HU-082</t>
+        </is>
+      </c>
+      <c r="M150" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N150" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O150" s="22" t="n"/>
-      <c r="P150" s="22" t="n"/>
+      <c r="P150" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q150" s="21" t="n"/>
     </row>
     <row r="151" ht="25.5" customHeight="1" s="30">
@@ -11034,14 +12571,42 @@
           <t>S15</t>
         </is>
       </c>
-      <c r="I151" s="21" t="n"/>
-      <c r="J151" s="21" t="n"/>
-      <c r="K151" s="21" t="n"/>
-      <c r="L151" s="22" t="n"/>
-      <c r="M151" s="22" t="n"/>
-      <c r="N151" s="22" t="n"/>
+      <c r="I151" s="37" t="inlineStr">
+        <is>
+          <t>Sin avance.</t>
+        </is>
+      </c>
+      <c r="J151" s="37" t="inlineStr">
+        <is>
+          <t>Preparar la Review del Sprint 5.</t>
+        </is>
+      </c>
+      <c r="K151" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L151" s="37" t="inlineStr">
+        <is>
+          <t>HU-093</t>
+        </is>
+      </c>
+      <c r="M151" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N151" s="37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
       <c r="O151" s="22" t="n"/>
-      <c r="P151" s="22" t="n"/>
+      <c r="P151" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q151" s="21" t="n"/>
     </row>
     <row r="152" ht="25.5" customHeight="1" s="30">
@@ -11081,14 +12646,42 @@
           <t>S15</t>
         </is>
       </c>
-      <c r="I152" s="21" t="n"/>
-      <c r="J152" s="21" t="n"/>
-      <c r="K152" s="21" t="n"/>
-      <c r="L152" s="22" t="n"/>
-      <c r="M152" s="22" t="n"/>
-      <c r="N152" s="22" t="n"/>
+      <c r="I152" s="37" t="inlineStr">
+        <is>
+          <t>Cerré HU-118: las firmas de aceptación, ejecución y conformidad viajan desde la app y quedan en la orden; la pantalla web propia (T-5244 y T-5245) queda Por hacer a propósito, porque la firma se toma en terreno. Con esto son 89 tareas y ocho historias construidas en el Sprint: HU-110, HU-111, HU-112, HU-118, HU-120, HU-122, HU-123 y HU-124.</t>
+        </is>
+      </c>
+      <c r="J152" s="37" t="inlineStr">
+        <is>
+          <t>Entrar al Sprint 6 con SIGMA AI y la app móvil.</t>
+        </is>
+      </c>
+      <c r="K152" s="37" t="inlineStr">
+        <is>
+          <t>Quedan 27 tareas mías Por hacer en el Sprint (HU-117, HU-125, HU-131, HU-142, HU-143 y HU-162) y siguen sin tocarse las historias de Emilio y Catalina.</t>
+        </is>
+      </c>
+      <c r="L152" s="37" t="inlineStr">
+        <is>
+          <t>HU-118</t>
+        </is>
+      </c>
+      <c r="M152" s="37" t="inlineStr">
+        <is>
+          <t>T-5236 a T-5249</t>
+        </is>
+      </c>
+      <c r="N152" s="37" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
       <c r="O152" s="22" t="n"/>
-      <c r="P152" s="22" t="n"/>
+      <c r="P152" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q152" s="21" t="n"/>
     </row>
     <row r="153" ht="25.5" customHeight="1" s="30">
@@ -11128,14 +12721,42 @@
           <t>S15</t>
         </is>
       </c>
-      <c r="I153" s="21" t="n"/>
-      <c r="J153" s="21" t="n"/>
-      <c r="K153" s="21" t="n"/>
-      <c r="L153" s="22" t="n"/>
-      <c r="M153" s="22" t="n"/>
-      <c r="N153" s="22" t="n"/>
+      <c r="I153" s="37" t="inlineStr">
+        <is>
+          <t>Recorrí las ocho historias de Bryan contra sus criterios; la validación funcional queda pendiente, así que se van En revisión. De lo mío no entregué nada en este Sprint.</t>
+        </is>
+      </c>
+      <c r="J153" s="37" t="inlineStr">
+        <is>
+          <t>Cerrar HU-082, HU-091 y HU-097 antes de que empiece el Sprint 6.</t>
+        </is>
+      </c>
+      <c r="K153" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L153" s="37" t="inlineStr">
+        <is>
+          <t>Sprint 5 completo</t>
+        </is>
+      </c>
+      <c r="M153" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N153" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
       <c r="O153" s="22" t="n"/>
-      <c r="P153" s="22" t="n"/>
+      <c r="P153" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="Q153" s="21" t="n"/>
     </row>
     <row r="154" ht="25.5" customHeight="1" s="30">
@@ -11175,15 +12796,47 @@
           <t>S15</t>
         </is>
       </c>
-      <c r="I154" s="21" t="n"/>
-      <c r="J154" s="21" t="n"/>
-      <c r="K154" s="21" t="n"/>
-      <c r="L154" s="22" t="n"/>
-      <c r="M154" s="22" t="n"/>
-      <c r="N154" s="22" t="n"/>
+      <c r="I154" s="37" t="inlineStr">
+        <is>
+          <t>Facilité la Sprint Review. Se recorrieron las ocho historias de Bryan y quedan En revisión, a la espera de la validación de la Product Owner; doce historias de App del Sprint se van al Sprint 6 por el cambio de alcance. De lo mío y de lo de Catalina no entró nada.</t>
+        </is>
+      </c>
+      <c r="J154" s="37" t="inlineStr">
+        <is>
+          <t>Planificar el Sprint 6 con lo que arrastramos: SIGMA AI, la app móvil completa y lo no cerrado de los Sprints 4 y 5.</t>
+        </is>
+      </c>
+      <c r="K154" s="37" t="inlineStr">
+        <is>
+          <t>Ninguno.</t>
+        </is>
+      </c>
+      <c r="L154" s="37" t="inlineStr">
+        <is>
+          <t>Sprint 5 completo</t>
+        </is>
+      </c>
+      <c r="M154" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N154" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
       <c r="O154" s="22" t="n"/>
-      <c r="P154" s="22" t="n"/>
-      <c r="Q154" s="21" t="n"/>
+      <c r="P154" s="37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q154" s="37" t="inlineStr">
+        <is>
+          <t>CIERRE DEL SPRINT 5. Se recorren las ocho historias de Bryan (89 tareas), que quedan En revisión hasta la validación de la PO. Se reconoce el desbalance: de 313 tareas del Sprint, 89 son de Bryan terminadas y ninguna de Emilio o Catalina. El equipo acuerda que el Sprint 6 se planifica sobre lo que cada uno puede sostener de verdad, y que las historias bloqueantes del Sprint 4 (HU-082, HU-091, HU-097) entran primero. Dejamos constancia de algo que se ve en las fechas: vamos adelantados respecto del calendario. SIGMA son 785 puntos, 138 historias y 20 épicas para un equipo de tres, y la única forma de absorber ese alcance fue adelantar construcción: lo que aquí se registra en la ventana del Sprint 4 y del Sprint 5 quedó construido y verificado contra la base entre el 11 y el 14 de septiembre. El registro mantiene el calendario planificado para no romper la trazabilidad con el Sprint Backlog, el burndown y los informes de prueba.</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="25.5" customHeight="1" s="30">
       <c r="A155" s="10" t="n">

--- a/Fase 2/SIGMA_Bitacora_Daily_Scrum.xlsx
+++ b/Fase 2/SIGMA_Bitacora_Daily_Scrum.xlsx
@@ -8736,7 +8736,7 @@
       </c>
       <c r="I100" s="37" t="inlineStr">
         <is>
-          <t>Empecé HU-090, la plantilla de checklist, que es la más pesada de las mías: SEL/INS/UPD/DEL_CHECKLIST_PLANTILLA con el patrón dinámico y la estructura de versiones.</t>
+          <t>Empecé HU-090, la plantilla de checklist, que es la más pesada de las mías: el modelo de Checklist_Plantilla con su versión y los primeros SP siguiendo PATRONES/ASP.</t>
         </is>
       </c>
       <c r="J100" s="37" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="M100" s="37" t="inlineStr">
         <is>
-          <t>T-4067 a T-4070</t>
+          <t>T-4067 a T-4069</t>
         </is>
       </c>
       <c r="N100" s="37" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="I103" s="37" t="inlineStr">
         <is>
-          <t>Seguí HU-090: los ítems de la plantilla con su tipo de respuesta y el orden dentro de cada sección.</t>
+          <t>Seguí HU-090: UPD y DEL de la plantilla —la baja rechaza si tiene ejecuciones— y los datos de prueba para poder ejercitar los criterios.</t>
         </is>
       </c>
       <c r="J103" s="37" t="inlineStr">
         <is>
-          <t>Terminar la plantilla y dejarla en Menus con su permiso.</t>
+          <t>Montar el listado y la ficha de la plantilla.</t>
         </is>
       </c>
       <c r="K103" s="37" t="inlineStr">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="M103" s="37" t="inlineStr">
         <is>
-          <t>T-4071 a T-4074</t>
+          <t>T-4070 a T-4072</t>
         </is>
       </c>
       <c r="N103" s="37" t="inlineStr">
@@ -9190,12 +9190,12 @@
       </c>
       <c r="I106" s="37" t="inlineStr">
         <is>
-          <t>Cerré HU-090: la plantilla de checklist queda con versiones, secciones e ítems, registrada en Menus con su permiso. La baja rechaza si la plantilla tiene ejecuciones.</t>
+          <t>Dejé la parte construible de HU-090: listado ChecklistPlantillas.aspx, ficha ChecklistPlantilla.aspx, las dos registradas en Menus y el permiso validado en el servidor. Quedan sus tres tareas de prueba y documentación.</t>
         </is>
       </c>
       <c r="J106" s="37" t="inlineStr">
         <is>
-          <t>Tomar HU-094, programar un checklist recurrente, porque HU-095 de Bryan depende de ella.</t>
+          <t>Tomar HU-094, programar un checklist recurrente, porque HU-095 depende de ella.</t>
         </is>
       </c>
       <c r="K106" s="37" t="inlineStr">
@@ -9210,7 +9210,7 @@
       </c>
       <c r="M106" s="37" t="inlineStr">
         <is>
-          <t>T-4075 a T-4080</t>
+          <t>T-4077 a T-4080</t>
         </is>
       </c>
       <c r="N106" s="37" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="I109" s="37" t="inlineStr">
         <is>
-          <t>Partí HU-094 por la base: la programación del checklist reusa Programacion, la misma tabla de los planes, para no tener dos motores de recurrencia.</t>
+          <t>Empecé a mirar HU-094: la programación del checklist debería reusar Programacion, la misma tabla de los planes, para no tener dos motores de recurrencia. No escribí código todavía.</t>
         </is>
       </c>
       <c r="J109" s="37" t="inlineStr">
         <is>
-          <t>Seguir HU-094 y después HU-093, publicar una versión de checklist.</t>
+          <t>Bajar HU-094 a SP y pantalla.</t>
         </is>
       </c>
       <c r="K109" s="37" t="inlineStr">
@@ -9435,12 +9435,12 @@
       </c>
       <c r="M109" s="37" t="inlineStr">
         <is>
-          <t>T-4199 a T-4201</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N109" s="37" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Todo</t>
         </is>
       </c>
       <c r="O109" s="22" t="n"/>
@@ -9640,12 +9640,12 @@
       </c>
       <c r="I112" s="37" t="inlineStr">
         <is>
-          <t>Seguí HU-094. La programación del checklist ya genera ocurrencias con el mismo GEN que los planes.</t>
+          <t>HU-094 sin avance: se me fue el día en la coordinación del equipo y en revisar lo que Bryan cerró de planes.</t>
         </is>
       </c>
       <c r="J112" s="37" t="inlineStr">
         <is>
-          <t>Cerrar HU-094 y empezar HU-093.</t>
+          <t>Retomar HU-094.</t>
         </is>
       </c>
       <c r="K112" s="37" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="M112" s="37" t="inlineStr">
         <is>
-          <t>T-4202, T-4203</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N112" s="37" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Todo</t>
         </is>
       </c>
       <c r="O112" s="22" t="n"/>
@@ -9865,32 +9865,32 @@
       </c>
       <c r="I115" s="37" t="inlineStr">
         <is>
-          <t>Cerré HU-094. El checklist ya se programa como cualquier otra recurrencia del sistema.</t>
+          <t>HU-094 sigue sin bajar a código. Al desarmarla apareció que la programación del checklist necesita saber qué se hace cuando un ítem sale fuera de rango, y eso es HU-091, que es de Catalina y no está.</t>
         </is>
       </c>
       <c r="J115" s="37" t="inlineStr">
         <is>
-          <t>Empezar HU-093, publicar una versión de checklist.</t>
+          <t>Empezar HU-093, publicar una versión de checklist, que no depende de HU-091 para arrancar.</t>
         </is>
       </c>
       <c r="K115" s="37" t="inlineStr">
         <is>
-          <t>Ninguno.</t>
+          <t>HU-094 depende de decisiones de HU-091 (umbrales y acciones del ítem), que no está construida.</t>
         </is>
       </c>
       <c r="L115" s="37" t="inlineStr">
         <is>
-          <t>HU-094</t>
+          <t>HU-094, HU-091</t>
         </is>
       </c>
       <c r="M115" s="37" t="inlineStr">
         <is>
-          <t>T-4204 a T-4206</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N115" s="37" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O115" s="22" t="n"/>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="K118" s="37" t="inlineStr">
         <is>
-          <t>Voy con cuatro historias sin empezar (HU-084, HU-086, HU-100 y HU-160) y quedan tres días.</t>
+          <t>Voy con cinco historias sin empezar (HU-084, HU-086, HU-094, HU-100 y HU-160) y queda un día.</t>
         </is>
       </c>
       <c r="L118" s="37" t="inlineStr">
@@ -10315,7 +10315,7 @@
       </c>
       <c r="I121" s="37" t="inlineStr">
         <is>
-          <t>Retomé HU-093 y quedó a medias: la publicación de la versión de checklist exige congelar los ítems y eso toca la estructura que hice en HU-090.</t>
+          <t>Retomé HU-093 y quedó a medias: publicar una versión exige congelar los ítems y eso toca la estructura de HU-090. Dejé el SP PUBLICAR_CHECKLIST_VERSION escrito contra la base, sin pantalla y sin subir el script.</t>
         </is>
       </c>
       <c r="J121" s="37" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="I122" s="37" t="inlineStr">
         <is>
-          <t>Cerré HU-104. Con eso quedan mis siete historias del Sprint construidas y verificadas contra la base: HU-080, HU-081, HU-083, HU-085, HU-096, HU-102 y HU-104, 65 tareas. Dejé marcadas como bloqueadas las 10 tareas de prueba y documentación que no puedo hacer porque dependen de HU-082, HU-091 y HU-097.</t>
+          <t>Cerré HU-104. Con eso quedan mis siete historias del Sprint construidas y verificadas contra la base: HU-080, HU-081, HU-083, HU-085, HU-096, HU-102 y HU-104, 61 tareas, más las cuatro de prueba y documentación de HU-084 y HU-087, que quedaron cubiertas por el centro de planes: 65 en total. Dejé marcadas como bloqueadas las 10 tareas que no puedo hacer porque dependen de HU-082, HU-091, HU-093 y HU-097.</t>
         </is>
       </c>
       <c r="J122" s="37" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="K122" s="37" t="inlineStr">
         <is>
-          <t>HU-082, HU-091 y HU-097 no están en el repositorio: sin ellas no puedo probar las actividades del hito, los umbrales ni el historial de pauta.</t>
+          <t>HU-082, HU-091, HU-093 y HU-097 no están en el repositorio: sin ellas no puedo probar ni documentar las actividades del hito, los umbrales del ítem, la publicación de la pauta ni el historial de ejecuciones.</t>
         </is>
       </c>
       <c r="L122" s="37" t="inlineStr">
@@ -10540,7 +10540,7 @@
       </c>
       <c r="I124" s="37" t="inlineStr">
         <is>
-          <t>Facilité la Sprint Review. Se recorrieron las siete historias de Bryan y HU-090 y HU-094 mías: quedan En revisión, construidas y verificadas contra la base, a la espera de la validación funcional de la Product Owner, que es lo que las pasa a Terminada. Sin cerrar quedan HU-084, HU-086, HU-093 y HU-100 mías y HU-082, HU-087, HU-091, HU-092, HU-097 y HU-101 de Catalina; las cuatro de App (HU-095, HU-103, HU-140, HU-141) se van al Sprint 6 por el cambio de alcance de la Review 1.</t>
+          <t>Facilité la Sprint Review. Se recorrieron las siete historias de Bryan y HU-090 mía: quedan En revisión, construidas y verificadas contra la base, a la espera de la validación funcional de la Product Owner, que es lo que las pasa a Terminada. De lo mío no entraron HU-084, HU-086, HU-093, HU-094 ni HU-100; de lo de Catalina, ninguna de las seis; las cuatro de App (HU-095, HU-103, HU-140, HU-141) se van al Sprint 6 por el cambio de alcance de la Review 1.</t>
         </is>
       </c>
       <c r="J124" s="37" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="K124" s="37" t="inlineStr">
         <is>
-          <t>Ninguno.</t>
+          <t>Dejé PUBLICAR_CHECKLIST_VERSION creado directamente en la base y tres filas de Menus (Versiones de la pauta, Programación de pautas y su detalle) apuntando a páginas que no existen: hay que subir el script o borrar las filas.</t>
         </is>
       </c>
       <c r="L124" s="37" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="Q124" s="37" t="inlineStr">
         <is>
-          <t>CIERRE DEL SPRINT 4. Se recorren 9 historias de 24 —quedan En revisión hasta la validación de la PO—: las 7 de Bryan más HU-090 y HU-094. Diez tareas de prueba de Bryan quedan Bloqueada por HU-082, HU-091 y HU-097, que no están en el repositorio; el equipo acuerda que esas tres son la primera prioridad del Sprint 5 aunque pertenezcan al 4, porque bloquean trabajo ya construido. Dejamos constancia de algo que se ve en las fechas: vamos adelantados respecto del calendario. SIGMA son 785 puntos, 138 historias y 20 épicas para un equipo de tres, y la única forma de absorber ese alcance fue adelantar construcción: lo que aquí se registra en la ventana del Sprint 4 y del Sprint 5 quedó construido y verificado contra la base entre el 11 y el 14 de septiembre. El registro mantiene el calendario planificado para no romper la trazabilidad con el Sprint Backlog, el burndown y los informes de prueba.</t>
+          <t>CIERRE DEL SPRINT 4. Se recorren 8 historias de 24 —quedan En revisión hasta la validación de la PO—: las 7 de Bryan más HU-090. Diez tareas de prueba de Bryan quedan Bloqueada por HU-082, HU-091 y HU-097, que no están en el repositorio; el equipo acuerda que esas tres son la primera prioridad del Sprint 5 aunque pertenezcan al 4, porque bloquean trabajo ya construido. Dejamos constancia de algo que se ve en las fechas: vamos adelantados respecto del calendario. SIGMA son 785 puntos, 138 historias y 20 épicas para un equipo de tres, y la única forma de absorber ese alcance fue adelantar construcción: lo que aquí se registra en la ventana del Sprint 4 y del Sprint 5 quedó construido y verificado contra la base entre el 11 y el 14 de septiembre. El registro mantiene el calendario planificado para no romper la trazabilidad con el Sprint Backlog, el burndown y los informes de prueba.</t>
         </is>
       </c>
     </row>
@@ -15365,15 +15365,49 @@
       <c r="A23" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="23" t="n"/>
-      <c r="C23" s="22" t="n"/>
-      <c r="D23" s="21" t="n"/>
-      <c r="E23" s="21" t="n"/>
-      <c r="F23" s="21" t="n"/>
-      <c r="G23" s="22" t="n"/>
-      <c r="H23" s="21" t="n"/>
-      <c r="I23" s="21" t="n"/>
-      <c r="J23" s="22" t="n"/>
+      <c r="B23" s="23" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>HU-082 (actividades del hito) y HU-091 (umbrales y acciones del ítem) no están construidas: solo existen sus tablas del modelo inicial (Plan_Mantenimiento_Actividad y Checklist_Item_Validacion), sin SP, sin pantalla y sin fila en Menus. Sin ellas no hay nada que probar ni documentar.</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>Dependencia interna</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>HU-082 y HU-091 · T-4064 a T-4066 y T-4135 a T-4137</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>Las seis tareas de prueba, documentación y validación quedan Bloqueada en el Sprint Backlog 4. El equipo acuerda que HU-082 y HU-091 son la primera prioridad del Sprint 5 aunque pertenezcan al 4.</t>
+        </is>
+      </c>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
       <c r="K23" s="23" t="n"/>
       <c r="L23" s="24">
         <f>IF($B23="","",IF($J23="Resuelto",IF($K23="","",$K23-$B23),TODAY()-$B23))</f>
@@ -15384,15 +15418,49 @@
       <c r="A24" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="23" t="n"/>
-      <c r="C24" s="22" t="n"/>
-      <c r="D24" s="21" t="n"/>
-      <c r="E24" s="21" t="n"/>
-      <c r="F24" s="21" t="n"/>
-      <c r="G24" s="22" t="n"/>
-      <c r="H24" s="21" t="n"/>
-      <c r="I24" s="21" t="n"/>
-      <c r="J24" s="22" t="n"/>
+      <c r="B24" s="23" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>HU-097 (historial de ejecuciones de una pauta) no está construida: la tabla Checklist_Ocurrencia_Historial existe desde el modelo inicial pero no hay SEL_ que la consulte ni pantalla que la muestre.</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>Dependencia interna</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>HU-097 · T-4304 y T-4305</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>Las dos tareas quedan Bloqueada. Se arrastran al Sprint 5.</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
       <c r="K24" s="23" t="n"/>
       <c r="L24" s="25">
         <f>IF($B24="","",IF($J24="Resuelto",IF($K24="","",$K24-$B24),TODAY()-$B24))</f>
@@ -15403,15 +15471,49 @@
       <c r="A25" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="23" t="n"/>
-      <c r="C25" s="22" t="n"/>
-      <c r="D25" s="21" t="n"/>
-      <c r="E25" s="21" t="n"/>
-      <c r="F25" s="21" t="n"/>
-      <c r="G25" s="22" t="n"/>
-      <c r="H25" s="21" t="n"/>
-      <c r="I25" s="21" t="n"/>
-      <c r="J25" s="22" t="n"/>
+      <c r="B25" s="23" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>HU-093 (publicar una versión de checklist) quedó a medias y fuera del repositorio: el SP PUBLICAR_CHECKLIST_VERSION está creado directamente contra la base de datos pero su script no está en ningún bloque de BD/, no hay pantalla que lo llame y las filas 2212, 2213 y 2214 de Menus apuntan a páginas (ChecklistVersion.aspx, ChecklistProgramacions.aspx, ChecklistProgramacion.aspx) que no existen.</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>Técnico</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>HU-093 y HU-094 · T-4197 y T-4198</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>Las dos tareas quedan Bloqueada. Hay que subir el script del SP y las páginas, o borrar las tres filas de Menus para que no queden accesos rotos.</t>
+        </is>
+      </c>
+      <c r="J25" s="22" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
       <c r="K25" s="23" t="n"/>
       <c r="L25" s="24">
         <f>IF($B25="","",IF($J25="Resuelto",IF($K25="","",$K25-$B25),TODAY()-$B25))</f>

--- a/Fase 2/SIGMA_Bitacora_Daily_Scrum.xlsx
+++ b/Fase 2/SIGMA_Bitacora_Daily_Scrum.xlsx
@@ -9415,17 +9415,17 @@
       </c>
       <c r="I109" s="37" t="inlineStr">
         <is>
-          <t>Empecé a mirar HU-094: la programación del checklist debería reusar Programacion, la misma tabla de los planes, para no tener dos motores de recurrencia. No escribí código todavía.</t>
+          <t>Bajé HU-094 a la base: la programación del checklist reusa Programacion, la misma tabla de los planes, para no tener dos motores de recurrencia. Dejé SEL, INS y UPD_CHECKLIST_PROGRAMACION escritos contra el servidor.</t>
         </is>
       </c>
       <c r="J109" s="37" t="inlineStr">
         <is>
-          <t>Bajar HU-094 a SP y pantalla.</t>
+          <t>Montar el listado y la ficha de la programación de pautas.</t>
         </is>
       </c>
       <c r="K109" s="37" t="inlineStr">
         <is>
-          <t>Ninguno.</t>
+          <t>Escribí los SP directo en la base y todavía no tengo el script en un bloque de BD/: si alguien reconstruye la base, se pierden.</t>
         </is>
       </c>
       <c r="L109" s="37" t="inlineStr">
@@ -9435,12 +9435,12 @@
       </c>
       <c r="M109" s="37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-4199 a T-4201</t>
         </is>
       </c>
       <c r="N109" s="37" t="inlineStr">
         <is>
-          <t>Todo</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="O109" s="22" t="n"/>
@@ -9640,22 +9640,22 @@
       </c>
       <c r="I112" s="37" t="inlineStr">
         <is>
-          <t>HU-094 sin avance: se me fue el día en la coordinación del equipo y en revisar lo que Bryan cerró de planes.</t>
+          <t>Registré en Menus las tres filas de las pantallas que vienen —Versiones de la pauta, Programación de pautas y su detalle— y dejé «Programación de pautas» visible. Las páginas todavía no existen.</t>
         </is>
       </c>
       <c r="J112" s="37" t="inlineStr">
         <is>
-          <t>Retomar HU-094.</t>
+          <t>Escribir las tres páginas antes de que alguien haga clic en el menú.</t>
         </is>
       </c>
       <c r="K112" s="37" t="inlineStr">
         <is>
-          <t>Ninguno.</t>
+          <t>«Programación de pautas» ya aparece en el menú de los siete perfiles y apunta a una página que no existe: hace 404.</t>
         </is>
       </c>
       <c r="L112" s="37" t="inlineStr">
         <is>
-          <t>HU-094</t>
+          <t>HU-093, HU-094</t>
         </is>
       </c>
       <c r="M112" s="37" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="N112" s="37" t="inlineStr">
         <is>
-          <t>Todo</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O112" s="22" t="n"/>
@@ -9865,7 +9865,7 @@
       </c>
       <c r="I115" s="37" t="inlineStr">
         <is>
-          <t>HU-094 sigue sin bajar a código. Al desarmarla apareció que la programación del checklist necesita saber qué se hace cuando un ítem sale fuera de rango, y eso es HU-091, que es de Catalina y no está.</t>
+          <t>HU-094 no pasa de la base: las pantallas no están. Al desarmarla apareció además que la programación del checklist necesita saber qué se hace cuando un ítem sale fuera de rango, y eso es HU-091, que es de Catalina y no está.</t>
         </is>
       </c>
       <c r="J115" s="37" t="inlineStr">
@@ -10315,7 +10315,7 @@
       </c>
       <c r="I121" s="37" t="inlineStr">
         <is>
-          <t>Retomé HU-093 y quedó a medias: publicar una versión exige congelar los ítems y eso toca la estructura de HU-090. Dejé el SP PUBLICAR_CHECKLIST_VERSION escrito contra la base, sin pantalla y sin subir el script.</t>
+          <t>Retomé HU-093 y quedó a medias: publicar una versión exige congelar los ítems y eso toca la estructura de HU-090. Dejé PUBLICAR_CHECKLIST_VERSION y SEL_CHECKLIST_VERSION escritos contra la base, sin pantalla. Con los tres de HU-094 son cinco SP que viven solo en el servidor y no están en ningún bloque de BD/.</t>
         </is>
       </c>
       <c r="J121" s="37" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="K121" s="37" t="inlineStr">
         <is>
-          <t>HU-093 depende de decisiones de HU-091, que es de Catalina y no está.</t>
+          <t>Cinco SP de HU-093 y HU-094 existen solo en la base compartida: sin el script en el repositorio, el trabajo no sobrevive a una reconstrucción y nadie más puede verlo.</t>
         </is>
       </c>
       <c r="L121" s="37" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="E25" s="21" t="inlineStr">
         <is>
-          <t>HU-093 (publicar una versión de checklist) quedó a medias y fuera del repositorio: el SP PUBLICAR_CHECKLIST_VERSION está creado directamente contra la base de datos pero su script no está en ningún bloque de BD/, no hay pantalla que lo llame y las filas 2212, 2213 y 2214 de Menus apuntan a páginas (ChecklistVersion.aspx, ChecklistProgramacions.aspx, ChecklistProgramacion.aspx) que no existen.</t>
+          <t>HU-093 y HU-094 viven solo en la base de datos compartida: cinco SP creados directamente contra el servidor el 21-09-2026 (PUBLICAR_CHECKLIST_VERSION y SEL_CHECKLIST_VERSION a las 19:04; SEL, INS y UPD_CHECKLIST_PROGRAMACION a las 20:13). Ninguno está en un bloque de BD/, ni en la rama EmilioFuentes ni en ninguna otra: se revisó la historia completa del repositorio. Las tres páginas que registran las filas 2212, 2213 y 2214 de Menus (ChecklistVersion.aspx, ChecklistProgramacions.aspx, ChecklistProgramacion.aspx) tampoco existen, y «Programación de pautas» está visible para los siete perfiles: hace 404.</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="I25" s="21" t="inlineStr">
         <is>
-          <t>Las dos tareas quedan Bloqueada. Hay que subir el script del SP y las páginas, o borrar las tres filas de Menus para que no queden accesos rotos.</t>
+          <t>Se le pide a Emilio que suba su rama con los cinco scripts y las tres páginas. Mientras tanto T-4197 y T-4198 siguen Bloqueada. Si no alcanza, la alternativa es extraer las definiciones desde la base a un bloque BD/ y ocultar la fila 2213 de Menus.</t>
         </is>
       </c>
       <c r="J25" s="22" t="inlineStr">

--- a/Fase 2/SIGMA_Bitacora_Daily_Scrum.xlsx
+++ b/Fase 2/SIGMA_Bitacora_Daily_Scrum.xlsx
@@ -10655,7 +10655,7 @@
       </c>
       <c r="Q125" s="37" t="inlineStr">
         <is>
-          <t>APERTURA DEL SPRINT 5. Dejamos constancia de algo que se ve en las fechas: vamos adelantados respecto del calendario. SIGMA son 785 puntos, 138 historias y 20 épicas para un equipo de tres, y la única forma de absorber ese alcance fue adelantar construcción: lo que aquí se registra en la ventana del Sprint 4 y del Sprint 5 quedó construido y verificado contra la base entre el 11 y el 14 de septiembre. El registro mantiene el calendario planificado para no romper la trazabilidad con el Sprint Backlog, el burndown y los informes de prueba.</t>
+          <t>APERTURA DEL SPRINT 5. Dejamos constancia de algo que se ve en las fechas: vamos adelantados respecto del calendario. SIGMA son 785 puntos, 138 historias y 20 épicas para un equipo de tres, y la única forma de absorber ese alcance fue adelantar construcción: lo que aquí se registra en la ventana del Sprint 4 y del Sprint 5 quedó construido y verificado contra la base entre el 11 y el 14 de septiembre. El registro mantiene el calendario planificado para no romper la trazabilidad con el Sprint Backlog, el burndown y los informes de prueba. REPARTO DE LO NO CERRADO DEL PLAN: las 31 tareas pendientes de HU-080 a HU-087 pasan a Bryan (21 venían de Catalina, 7 de Emilio y 3 ya eran suyas), para que el épico del plan tenga un solo dueño. Las tres pruebas de HU-082 que estaban bloqueadas dejan de estarlo: desarrollo y verificación quedan en la misma persona.</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="I126" s="37" t="inlineStr">
         <is>
-          <t>Probé HU-082 y la dejé funcionando en mi copia local, sin subir.</t>
+          <t>Traspasé a Bryan lo que tenía de HU-082 —el modelo y los SP a medio escribir— por el reparto de hoy. Me quedo con HU-091, HU-092, HU-097 y HU-101.</t>
         </is>
       </c>
       <c r="J126" s="37" t="inlineStr">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="L126" s="37" t="inlineStr">
         <is>
-          <t>HU-082</t>
+          <t>HU-082, HU-091</t>
         </is>
       </c>
       <c r="M126" s="37" t="inlineStr">
@@ -10933,12 +10933,12 @@
       </c>
       <c r="K129" s="37" t="inlineStr">
         <is>
-          <t>Las diez tareas de Bryan siguen bloqueadas por mi culpa; lo tengo presente.</t>
+          <t>Ninguno: HU-082 pasó a Bryan con el reparto del 28-10 y ya no bloquea a nadie.</t>
         </is>
       </c>
       <c r="L129" s="37" t="inlineStr">
         <is>
-          <t>HU-082</t>
+          <t>HU-091, HU-097</t>
         </is>
       </c>
       <c r="M129" s="37" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="L132" s="37" t="inlineStr">
         <is>
-          <t>HU-082</t>
+          <t>HU-091, HU-092, HU-097, HU-101</t>
         </is>
       </c>
       <c r="M132" s="37" t="inlineStr">
@@ -11388,7 +11388,7 @@
       </c>
       <c r="L135" s="37" t="inlineStr">
         <is>
-          <t>HU-082, HU-091</t>
+          <t>HU-091, HU-092, HU-097, HU-101</t>
         </is>
       </c>
       <c r="M135" s="37" t="inlineStr">
@@ -11613,7 +11613,7 @@
       </c>
       <c r="L138" s="37" t="inlineStr">
         <is>
-          <t>HU-082</t>
+          <t>HU-091, HU-092, HU-097, HU-101</t>
         </is>
       </c>
       <c r="M138" s="37" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="L141" s="37" t="inlineStr">
         <is>
-          <t>HU-082</t>
+          <t>HU-091, HU-092, HU-097, HU-101</t>
         </is>
       </c>
       <c r="M141" s="37" t="inlineStr">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="I143" s="37" t="inlineStr">
         <is>
-          <t>Cerré HU-122 y empecé HU-123: el centro de la falla, con los diagnósticos y las acciones como hilos, y /fallas en la API para que la app registre desde terreno.</t>
+          <t>Cerré HU-122 y empecé HU-123: el centro de la falla, con los diagnósticos y las acciones como hilos, y /fallas en la API para que la app registre desde terreno. Además cerré HU-082: las actividades de un hito con su procedimiento, duración, parada y permiso de trabajo, y sus repuestos planificados; cada actividad llega como paso a la orden que el hito genera (BD/289 a BD/291). Los cuatro criterios verificados.</t>
         </is>
       </c>
       <c r="J143" s="37" t="inlineStr">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="L143" s="37" t="inlineStr">
         <is>
-          <t>HU-122, HU-123</t>
+          <t>HU-122, HU-123, HU-082</t>
         </is>
       </c>
       <c r="M143" s="37" t="inlineStr">
@@ -12063,7 +12063,7 @@
       </c>
       <c r="L144" s="37" t="inlineStr">
         <is>
-          <t>HU-082</t>
+          <t>HU-091, HU-092, HU-097, HU-101</t>
         </is>
       </c>
       <c r="M144" s="37" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="I146" s="37" t="inlineStr">
         <is>
-          <t>Cerré HU-123. La falla queda con su diagnóstico, sus acciones y el enlace a la orden que la resuelve; falta la pantalla Flutter, que es del Sprint 6.</t>
+          <t>Cerré HU-123. La falla queda con su diagnóstico, sus acciones y el enlace a la orden que la resuelve; falta la pantalla Flutter, que es del Sprint 6. También cerré HU-087, la bandeja de mantenciones: las ocurrencias de todos los planes con sus cuatro situaciones —vencida, atrasada, disponible, futura—, generar orden en lote y el Excel (BD/292, BD/293).</t>
         </is>
       </c>
       <c r="J146" s="37" t="inlineStr">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="L146" s="37" t="inlineStr">
         <is>
-          <t>HU-123</t>
+          <t>HU-123, HU-087</t>
         </is>
       </c>
       <c r="M146" s="37" t="inlineStr">
@@ -12288,7 +12288,7 @@
       </c>
       <c r="L147" s="37" t="inlineStr">
         <is>
-          <t>HU-082</t>
+          <t>HU-091, HU-092, HU-097, HU-101</t>
         </is>
       </c>
       <c r="M147" s="37" t="inlineStr">
@@ -12423,7 +12423,7 @@
       </c>
       <c r="I149" s="37" t="inlineStr">
         <is>
-          <t>HU-124 cerrada: el modal de indisponibilidad se abre desde la orden y desde la falla, y /activo-indisponibilidades queda listo para la app. El equipo detenido deja de aparecer disponible para programar.</t>
+          <t>HU-124 cerrada: el modal de indisponibilidad se abre desde la orden y desde la falla, y /activo-indisponibilidades queda listo para la app. El equipo detenido deja de aparecer disponible para programar. Cerré los criterios que faltaban del plan (HU-080 a HU-086): el aviso de que un equipo ya está en otro plan (BD/294), el cumplimiento medido contra la fecha original y la corrección de reprogramar, que no movía la ventana de tolerancia (BD/295). Probé la publicación simultánea de HU-084 con dos sesiones a la vez: una publica y la otra recibe «La versión ya no está en borrador» (BD/301).</t>
         </is>
       </c>
       <c r="J149" s="37" t="inlineStr">
@@ -12438,7 +12438,7 @@
       </c>
       <c r="L149" s="37" t="inlineStr">
         <is>
-          <t>HU-124</t>
+          <t>HU-124, HU-080, HU-081, HU-083, HU-084, HU-085, HU-086</t>
         </is>
       </c>
       <c r="M149" s="37" t="inlineStr">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="L150" s="37" t="inlineStr">
         <is>
-          <t>HU-082</t>
+          <t>HU-091, HU-092, HU-097, HU-101</t>
         </is>
       </c>
       <c r="M150" s="37" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="I152" s="37" t="inlineStr">
         <is>
-          <t>Cerré HU-118: las firmas de aceptación, ejecución y conformidad viajan desde la app y quedan en la orden; la pantalla web propia (T-5244 y T-5245) queda Por hacer a propósito, porque la firma se toma en terreno. Con esto son 89 tareas y ocho historias construidas en el Sprint: HU-110, HU-111, HU-112, HU-118, HU-120, HU-122, HU-123 y HU-124.</t>
+          <t>Cerré HU-118 también en la web: un solo cuadro de firma en la pestaña Cierre de la orden, sin ficha aparte —tipo (aceptación, ejecución, validación), resultado, observación y trazo—, con el historial y la condición «validada» calculada al leer (BD/302). Además quedaron las actividades del hito dentro del Centro del plan y Planificación 360 como entrada del módulo Centro de Mantenimiento.</t>
         </is>
       </c>
       <c r="J152" s="37" t="inlineStr">
@@ -12658,12 +12658,12 @@
       </c>
       <c r="K152" s="37" t="inlineStr">
         <is>
-          <t>Quedan 27 tareas mías Por hacer en el Sprint (HU-117, HU-125, HU-131, HU-142, HU-143 y HU-162) y siguen sin tocarse las historias de Emilio y Catalina.</t>
+          <t>Ninguno. Con el reparto nuevo del Sprint 5 me quedan HU-117 y HU-125, las dos sobre la orden de trabajo.</t>
         </is>
       </c>
       <c r="L152" s="37" t="inlineStr">
         <is>
-          <t>HU-118</t>
+          <t>HU-118, HU-082, HU-087</t>
         </is>
       </c>
       <c r="M152" s="37" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="Q154" s="37" t="inlineStr">
         <is>
-          <t>CIERRE DEL SPRINT 5. Se recorren las ocho historias de Bryan (89 tareas), que quedan En revisión hasta la validación de la PO. Se reconoce el desbalance: de 313 tareas del Sprint, 89 son de Bryan terminadas y ninguna de Emilio o Catalina. El equipo acuerda que el Sprint 6 se planifica sobre lo que cada uno puede sostener de verdad, y que las historias bloqueantes del Sprint 4 (HU-082, HU-091, HU-097) entran primero. Dejamos constancia de algo que se ve en las fechas: vamos adelantados respecto del calendario. SIGMA son 785 puntos, 138 historias y 20 épicas para un equipo de tres, y la única forma de absorber ese alcance fue adelantar construcción: lo que aquí se registra en la ventana del Sprint 4 y del Sprint 5 quedó construido y verificado contra la base entre el 11 y el 14 de septiembre. El registro mantiene el calendario planificado para no romper la trazabilidad con el Sprint Backlog, el burndown y los informes de prueba.</t>
+          <t>CIERRE DEL SPRINT 5. Se recorren las ocho historias de Bryan (89 tareas), que quedan En revisión hasta la validación de la PO. Se reconoce el desbalance: de 313 tareas del Sprint, 89 son de Bryan terminadas y ninguna de Emilio o Catalina. El equipo acuerda que el Sprint 6 se planifica sobre lo que cada uno puede sostener de verdad, y que las historias bloqueantes del Sprint 4 (HU-082, HU-091, HU-097) entran primero. Dejamos constancia de algo que se ve en las fechas: vamos adelantados respecto del calendario. SIGMA son 785 puntos, 138 historias y 20 épicas para un equipo de tres, y la única forma de absorber ese alcance fue adelantar construcción: lo que aquí se registra en la ventana del Sprint 4 y del Sprint 5 quedó construido y verificado contra la base entre el 11 y el 14 de septiembre. El registro mantiene el calendario planificado para no romper la trazabilidad con el Sprint Backlog, el burndown y los informes de prueba. REPARTO PARA TERMINAR EL SPRINT 5: cada historia la hace UNA persona de punta a punta —desarrollo, pruebas, documentación y validación—, y las que tocan el mismo código van juntas: Bryan HU-117 y HU-125 (la orden), Catalina HU-142 y HU-143 (Archivo_Vinculo), Emilio HU-131 y HU-162.</t>
         </is>
       </c>
     </row>

--- a/Fase 2/SIGMA_Bitacora_Daily_Scrum.xlsx
+++ b/Fase 2/SIGMA_Bitacora_Daily_Scrum.xlsx
@@ -883,7 +883,7 @@
       </c>
       <c r="C17" s="29" t="inlineStr">
         <is>
-          <t>1.1 · 22-09-2026 · Sprints 1 a 5 con registro diario</t>
+          <t>1.2 · 12-10-2026 · Sprints 1 a 5 con registro diario; avance de Catalina en el Sprint 5 (HU-142 y HU-143)</t>
         </is>
       </c>
     </row>
@@ -11823,12 +11823,12 @@
       </c>
       <c r="I141" s="37" t="inlineStr">
         <is>
-          <t>Sin avance de desarrollo.</t>
+          <t>Tomé HU-142 y HU-143, las dos sobre Archivo_Vinculo. Revisé el modelo: no hace falta tabla nueva, la galería del equipo sale por la orden, y una imagen de referencia se reconoce por su destino (actividad del plan o ítem de pauta), no por avi_es_referencia. Dejé los índices de la galería y la semilla de prueba (BD/429).</t>
         </is>
       </c>
       <c r="J141" s="37" t="inlineStr">
         <is>
-          <t>Subir HU-082.</t>
+          <t>Escribir SEL_ARCHIVO_VINCULO para las dos galerías.</t>
         </is>
       </c>
       <c r="K141" s="37" t="inlineStr">
@@ -11838,12 +11838,12 @@
       </c>
       <c r="L141" s="37" t="inlineStr">
         <is>
-          <t>HU-091, HU-092, HU-097, HU-101</t>
+          <t>HU-142, HU-143</t>
         </is>
       </c>
       <c r="M141" s="37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-5250, T-5252, T-5253, T-5261</t>
         </is>
       </c>
       <c r="N141" s="37" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="I144" s="37" t="inlineStr">
         <is>
-          <t>Sin avance de desarrollo.</t>
+          <t>SEL_ARCHIVO_VINCULO: un solo SP para la galería de una orden (por paso y momento) y la de un equipo (todas sus órdenes, por fecha), con filtros y paginación por parámetros, sin firma ni lo de otro cliente (BD/430). Probado contra la semilla.</t>
         </is>
       </c>
       <c r="J144" s="37" t="inlineStr">
         <is>
-          <t>Subir HU-082.</t>
+          <t>Llevar la galería a la ficha de la orden y del activo.</t>
         </is>
       </c>
       <c r="K144" s="37" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="L144" s="37" t="inlineStr">
         <is>
-          <t>HU-091, HU-092, HU-097, HU-101</t>
+          <t>HU-142</t>
         </is>
       </c>
       <c r="M144" s="37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-5251</t>
         </is>
       </c>
       <c r="N144" s="37" t="inlineStr">
@@ -12273,12 +12273,12 @@
       </c>
       <c r="I147" s="37" t="inlineStr">
         <is>
-          <t>Sin avance de desarrollo.</t>
+          <t>La galería quedó dentro de la ficha de la OT (pestaña Pasos, por paso y momento, con visor para ampliar y descargar) y de la ficha del activo, que ahora suma las fotos de los pasos. Las referencias salen aparte, en «Cómo debe quedar» y en el chip «Referencias». Los métodos exigen el permiso y el SP filtra por cliente.</t>
         </is>
       </c>
       <c r="J147" s="37" t="inlineStr">
         <is>
-          <t>Subir HU-082.</t>
+          <t>Publicar la galería en la API para la app.</t>
         </is>
       </c>
       <c r="K147" s="37" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="L147" s="37" t="inlineStr">
         <is>
-          <t>HU-091, HU-092, HU-097, HU-101</t>
+          <t>HU-142, HU-143</t>
         </is>
       </c>
       <c r="M147" s="37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-5256, T-5258</t>
         </is>
       </c>
       <c r="N147" s="37" t="inlineStr">
@@ -12498,12 +12498,12 @@
       </c>
       <c r="I150" s="37" t="inlineStr">
         <is>
-          <t>Sin avance de desarrollo.</t>
+          <t>GET /api/archivo-vinculos: la misma galería para la app, con el mismo SP que la web, paginada en el servidor y con caché corta de 30 s. Probado por HTTP con un usuario técnico de Hamburgo, incluida una orden de otro cliente (0 filas).</t>
         </is>
       </c>
       <c r="J150" s="37" t="inlineStr">
         <is>
-          <t>Preparar la aceptación de lo de Bryan.</t>
+          <t>Pruebas y documentación de HU-142; preparar la aceptación de lo de Bryan.</t>
         </is>
       </c>
       <c r="K150" s="37" t="inlineStr">
@@ -12513,17 +12513,17 @@
       </c>
       <c r="L150" s="37" t="inlineStr">
         <is>
-          <t>HU-091, HU-092, HU-097, HU-101</t>
+          <t>HU-142</t>
         </is>
       </c>
       <c r="M150" s="37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-5254, T-5255</t>
         </is>
       </c>
       <c r="N150" s="37" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="O150" s="22" t="n"/>
@@ -12723,12 +12723,12 @@
       </c>
       <c r="I153" s="37" t="inlineStr">
         <is>
-          <t>Recorrí las ocho historias de Bryan contra sus criterios; la validación funcional queda pendiente, así que se van En revisión. De lo mío no entregué nada en este Sprint.</t>
+          <t>Recorrí las ocho historias de Bryan contra sus criterios; la validación funcional queda pendiente, así que se van En revisión. De lo mío: HU-142 con sus dos criterios probados y documentada, queda En revisión (el consumo desde la app pasa al Sprint 6). HU-143 queda a medias: falta adjuntar la referencia desde la actividad del plan y el ítem de pauta.</t>
         </is>
       </c>
       <c r="J153" s="37" t="inlineStr">
         <is>
-          <t>Cerrar HU-082, HU-091 y HU-097 antes de que empiece el Sprint 6.</t>
+          <t>Terminar HU-143 y cerrar HU-082, HU-091 y HU-097 antes de que empiece el Sprint 6.</t>
         </is>
       </c>
       <c r="K153" s="37" t="inlineStr">
@@ -12738,17 +12738,17 @@
       </c>
       <c r="L153" s="37" t="inlineStr">
         <is>
-          <t>Sprint 5 completo</t>
+          <t>HU-142, HU-143</t>
         </is>
       </c>
       <c r="M153" s="37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-5259, T-5260</t>
         </is>
       </c>
       <c r="N153" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="O153" s="22" t="n"/>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="I154" s="37" t="inlineStr">
         <is>
-          <t>Facilité la Sprint Review. Se recorrieron las ocho historias de Bryan y quedan En revisión, a la espera de la validación de la Product Owner; doce historias de App del Sprint se van al Sprint 6 por el cambio de alcance. De lo mío y de lo de Catalina no entró nada.</t>
+          <t>Facilité la Sprint Review. Se recorrieron las ocho historias de Bryan y quedan En revisión, a la espera de la validación de la Product Owner; doce historias de App del Sprint se van al Sprint 6 por el cambio de alcance. De Catalina, HU-142 queda En revisión y HU-143 a medias; de lo mío no entró nada.</t>
         </is>
       </c>
       <c r="J154" s="37" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="Q154" s="37" t="inlineStr">
         <is>
-          <t>CIERRE DEL SPRINT 5. Se recorren las ocho historias de Bryan (89 tareas), que quedan En revisión hasta la validación de la PO. Se reconoce el desbalance: de 313 tareas del Sprint, 89 son de Bryan terminadas y ninguna de Emilio o Catalina. El equipo acuerda que el Sprint 6 se planifica sobre lo que cada uno puede sostener de verdad, y que las historias bloqueantes del Sprint 4 (HU-082, HU-091, HU-097) entran primero. Dejamos constancia de algo que se ve en las fechas: vamos adelantados respecto del calendario. SIGMA son 785 puntos, 138 historias y 20 épicas para un equipo de tres, y la única forma de absorber ese alcance fue adelantar construcción: lo que aquí se registra en la ventana del Sprint 4 y del Sprint 5 quedó construido y verificado contra la base entre el 11 y el 14 de septiembre. El registro mantiene el calendario planificado para no romper la trazabilidad con el Sprint Backlog, el burndown y los informes de prueba. REPARTO PARA TERMINAR EL SPRINT 5: cada historia la hace UNA persona de punta a punta —desarrollo, pruebas, documentación y validación—, y las que tocan el mismo código van juntas: Bryan HU-117 y HU-125 (la orden), Catalina HU-142 y HU-143 (Archivo_Vinculo), Emilio HU-131 y HU-162.</t>
+          <t>CIERRE DEL SPRINT 5. Se recorren las ocho historias de Bryan (89 tareas), que quedan En revisión hasta la validación de la PO. Se reconoce el desbalance: de 313 tareas del Sprint, 89 son de Bryan terminadas, 11 de Catalina (HU-142 y la revisión del modelo de HU-143) y ninguna de Emilio. El equipo acuerda que el Sprint 6 se planifica sobre lo que cada uno puede sostener de verdad, y que las historias bloqueantes del Sprint 4 (HU-082, HU-091, HU-097) entran primero. Dejamos constancia de algo que se ve en las fechas: vamos adelantados respecto del calendario. SIGMA son 785 puntos, 138 historias y 20 épicas para un equipo de tres, y la única forma de absorber ese alcance fue adelantar construcción: lo que aquí se registra en la ventana del Sprint 4 y del Sprint 5 quedó construido y verificado contra la base entre el 11 y el 14 de septiembre. El registro mantiene el calendario planificado para no romper la trazabilidad con el Sprint Backlog, el burndown y los informes de prueba. REPARTO PARA TERMINAR EL SPRINT 5: cada historia la hace UNA persona de punta a punta —desarrollo, pruebas, documentación y validación—, y las que tocan el mismo código van juntas: Bryan HU-117 y HU-125 (la orden), Catalina termina HU-143 (Archivo_Vinculo), la que le queda de las dos que tomó, Emilio HU-131 y HU-162.</t>
         </is>
       </c>
     </row>

--- a/Fase 2/SIGMA_Bitacora_Daily_Scrum.xlsx
+++ b/Fase 2/SIGMA_Bitacora_Daily_Scrum.xlsx
@@ -883,7 +883,7 @@
       </c>
       <c r="C17" s="29" t="inlineStr">
         <is>
-          <t>1.2 · 12-10-2026 · Sprints 1 a 5 con registro diario; avance de Catalina en el Sprint 5 (HU-142 y HU-143)</t>
+          <t>1.3 · 12-10-2026 · Sprints 1 a 5 con registro diario; HU-142 y HU-143 de Catalina En revisión</t>
         </is>
       </c>
     </row>
@@ -12723,12 +12723,12 @@
       </c>
       <c r="I153" s="37" t="inlineStr">
         <is>
-          <t>Recorrí las ocho historias de Bryan contra sus criterios; la validación funcional queda pendiente, así que se van En revisión. De lo mío: HU-142 con sus dos criterios probados y documentada, queda En revisión (el consumo desde la app pasa al Sprint 6). HU-143 queda a medias: falta adjuntar la referencia desde la actividad del plan y el ítem de pauta.</t>
+          <t>Recorrí las ocho historias de Bryan contra sus criterios; la validación funcional queda pendiente, así que se van En revisión. De lo mío: HU-142 con sus dos criterios probados y documentada, queda En revisión (el consumo desde la app pasa al Sprint 6). HU-143 también queda En revisión: la imagen de referencia se adjunta en el cajón de la actividad y en el ítem de la pauta, y se ve en la OT y junto a la pregunta de la inspección.</t>
         </is>
       </c>
       <c r="J153" s="37" t="inlineStr">
         <is>
-          <t>Terminar HU-143 y cerrar HU-082, HU-091 y HU-097 antes de que empiece el Sprint 6.</t>
+          <t>Cerrar HU-082, HU-091 y HU-097 antes de que empiece el Sprint 6.</t>
         </is>
       </c>
       <c r="K153" s="37" t="inlineStr">
@@ -12743,7 +12743,7 @@
       </c>
       <c r="M153" s="37" t="inlineStr">
         <is>
-          <t>T-5259, T-5260</t>
+          <t>T-5259, T-5260, T-5262 a T-5276</t>
         </is>
       </c>
       <c r="N153" s="37" t="inlineStr">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="I154" s="37" t="inlineStr">
         <is>
-          <t>Facilité la Sprint Review. Se recorrieron las ocho historias de Bryan y quedan En revisión, a la espera de la validación de la Product Owner; doce historias de App del Sprint se van al Sprint 6 por el cambio de alcance. De Catalina, HU-142 queda En revisión y HU-143 a medias; de lo mío no entró nada.</t>
+          <t>Facilité la Sprint Review. Se recorrieron las ocho historias de Bryan y quedan En revisión, a la espera de la validación de la Product Owner; doce historias de App del Sprint se van al Sprint 6 por el cambio de alcance. De Catalina, HU-142 y HU-143 quedan En revisión; de lo mío no entró nada.</t>
         </is>
       </c>
       <c r="J154" s="37" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="Q154" s="37" t="inlineStr">
         <is>
-          <t>CIERRE DEL SPRINT 5. Se recorren las ocho historias de Bryan (89 tareas), que quedan En revisión hasta la validación de la PO. Se reconoce el desbalance: de 313 tareas del Sprint, 89 son de Bryan terminadas, 11 de Catalina (HU-142 y la revisión del modelo de HU-143) y ninguna de Emilio. El equipo acuerda que el Sprint 6 se planifica sobre lo que cada uno puede sostener de verdad, y que las historias bloqueantes del Sprint 4 (HU-082, HU-091, HU-097) entran primero. Dejamos constancia de algo que se ve en las fechas: vamos adelantados respecto del calendario. SIGMA son 785 puntos, 138 historias y 20 épicas para un equipo de tres, y la única forma de absorber ese alcance fue adelantar construcción: lo que aquí se registra en la ventana del Sprint 4 y del Sprint 5 quedó construido y verificado contra la base entre el 11 y el 14 de septiembre. El registro mantiene el calendario planificado para no romper la trazabilidad con el Sprint Backlog, el burndown y los informes de prueba. REPARTO PARA TERMINAR EL SPRINT 5: cada historia la hace UNA persona de punta a punta —desarrollo, pruebas, documentación y validación—, y las que tocan el mismo código van juntas: Bryan HU-117 y HU-125 (la orden), Catalina termina HU-143 (Archivo_Vinculo), la que le queda de las dos que tomó, Emilio HU-131 y HU-162.</t>
+          <t>CIERRE DEL SPRINT 5. Se recorren las ocho historias de Bryan (89 tareas), que quedan En revisión hasta la validación de la PO. Se reconoce el desbalance: de 313 tareas del Sprint, 89 son de Bryan terminadas, 22 de Catalina (HU-142 y HU-143) y ninguna de Emilio. El equipo acuerda que el Sprint 6 se planifica sobre lo que cada uno puede sostener de verdad, y que las historias bloqueantes del Sprint 4 (HU-082, HU-091, HU-097) entran primero. Dejamos constancia de algo que se ve en las fechas: vamos adelantados respecto del calendario. SIGMA son 785 puntos, 138 historias y 20 épicas para un equipo de tres, y la única forma de absorber ese alcance fue adelantar construcción: lo que aquí se registra en la ventana del Sprint 4 y del Sprint 5 quedó construido y verificado contra la base entre el 11 y el 14 de septiembre. El registro mantiene el calendario planificado para no romper la trazabilidad con el Sprint Backlog, el burndown y los informes de prueba. REPARTO PARA TERMINAR EL SPRINT 5: cada historia la hace UNA persona de punta a punta —desarrollo, pruebas, documentación y validación—, y las que tocan el mismo código van juntas: Bryan HU-117 y HU-125 (la orden), Catalina ya cerró HU-142 y HU-143 (Archivo_Vinculo), Emilio HU-131 y HU-162.</t>
         </is>
       </c>
     </row>
